--- a/progression_odds_all.xlsx
+++ b/progression_odds_all.xlsx
@@ -39,16 +39,16 @@
     <t>io_mono</t>
   </si>
   <si>
-    <t>firstlinechemotherapy</t>
+    <t>firstlinechemothe~y</t>
   </si>
   <si>
-    <t>nonfirstlinechemotherapy</t>
+    <t>nonfirstlinechemo~y</t>
   </si>
   <si>
-    <t>otherfirstlinetherapy</t>
+    <t>otherfirstlinethe~y</t>
   </si>
   <si>
-    <t>firstlinecombinationtherapy</t>
+    <t>firstlinecombinat~y</t>
   </si>
   <si>
     <t>antibrafdrug</t>
@@ -60,10 +60,10 @@
     <t>metinhibitor</t>
   </si>
   <si>
-    <t>carboplatinmonotherapy</t>
+    <t>carboplatinmonoth~y</t>
   </si>
   <si>
-    <t>cisplatinmonotherapy</t>
+    <t>cisplatinmonother~y</t>
   </si>
   <si>
     <t>antialkdrug#alk</t>
@@ -105,10 +105,10 @@
     <t>ecog4</t>
   </si>
   <si>
-    <t>squamouscellcarcinoma</t>
+    <t>squamouscellcarci~a</t>
   </si>
   <si>
-    <t>nonsquamouscellcarcinoma</t>
+    <t>nonsquamouscellca~a</t>
   </si>
   <si>
     <t>pdl1</t>
@@ -141,13 +141,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>daysfromadvanceddiagnosistotreat</t>
+    <t>daysfromadvancedd~t</t>
   </si>
   <si>
-    <t>patientassistanceprogram</t>
+    <t>patientassistance~m</t>
   </si>
   <si>
-    <t>othergovernmentalinsurance</t>
+    <t>othergovernmental~e</t>
   </si>
   <si>
     <t>medicare</t>
@@ -159,7 +159,7 @@
     <t>medicaid</t>
   </si>
   <si>
-    <t>commercialhealthplan</t>
+    <t>commercialhealthp~n</t>
   </si>
   <si>
     <t>noinsurance</t>
@@ -186,7 +186,7 @@
     <t>neversmoker</t>
   </si>
   <si>
-    <t>academicmedicalcenter</t>
+    <t>academicmedicalce~r</t>
   </si>
   <si>
     <t>kidney_bool</t>
@@ -195,10 +195,10 @@
     <t>liver_bool</t>
   </si>
   <si>
-    <t>connective_tissue_bool</t>
+    <t>connective_tissue~l</t>
   </si>
   <si>
-    <t>interstitiallungdisease</t>
+    <t>interstitiallungd~e</t>
   </si>
   <si>
     <t>diabetes</t>
@@ -213,28 +213,28 @@
     <t>othercnsmetastases</t>
   </si>
   <si>
-    <t>digestivesystemmetastases</t>
+    <t>digestivesystemme~s</t>
   </si>
   <si>
     <t>adrenalmetastases</t>
   </si>
   <si>
-    <t>unspecifiedmetastases</t>
+    <t>unspecifiedmetast~s</t>
   </si>
   <si>
-    <t>antiinfectiveusepriortotreatment</t>
+    <t>antiinfectiveusep~t</t>
   </si>
   <si>
-    <t>glucocorticoidusepriortotreatmen</t>
+    <t>glucocorticoiduse~n</t>
   </si>
   <si>
-    <t>clinicalstudydrugused</t>
+    <t>clinicalstudydrug~d</t>
   </si>
   <si>
     <t>bevacizumabused</t>
   </si>
   <si>
-    <t>threeormorechemotherapydrugs</t>
+    <t>threeormorechemot~s</t>
   </si>
   <si>
     <t>pdl1reported</t>

--- a/progression_odds_all.xlsx
+++ b/progression_odds_all.xlsx
@@ -39,16 +39,16 @@
     <t>io_mono</t>
   </si>
   <si>
-    <t>firstlinechemothe~y</t>
+    <t>firstlinechemotherapy</t>
   </si>
   <si>
-    <t>nonfirstlinechemo~y</t>
+    <t>nonfirstlinechemotherapy</t>
   </si>
   <si>
-    <t>otherfirstlinethe~y</t>
+    <t>otherfirstlinetherapy</t>
   </si>
   <si>
-    <t>firstlinecombinat~y</t>
+    <t>firstlinecombinationtherapy</t>
   </si>
   <si>
     <t>antibrafdrug</t>
@@ -60,10 +60,10 @@
     <t>metinhibitor</t>
   </si>
   <si>
-    <t>carboplatinmonoth~y</t>
+    <t>carboplatinmonotherapy</t>
   </si>
   <si>
-    <t>cisplatinmonother~y</t>
+    <t>cisplatinmonotherapy</t>
   </si>
   <si>
     <t>antialkdrug#alk</t>
@@ -105,10 +105,10 @@
     <t>ecog4</t>
   </si>
   <si>
-    <t>squamouscellcarci~a</t>
+    <t>squamouscellcarcinoma</t>
   </si>
   <si>
-    <t>nonsquamouscellca~a</t>
+    <t>nonsquamouscellcarcinoma</t>
   </si>
   <si>
     <t>pdl1</t>
@@ -141,13 +141,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>daysfromadvancedd~t</t>
+    <t>daysfromadvanceddiagnosistotreat</t>
   </si>
   <si>
-    <t>patientassistance~m</t>
+    <t>patientassistanceprogram</t>
   </si>
   <si>
-    <t>othergovernmental~e</t>
+    <t>othergovernmentalinsurance</t>
   </si>
   <si>
     <t>medicare</t>
@@ -159,7 +159,7 @@
     <t>medicaid</t>
   </si>
   <si>
-    <t>commercialhealthp~n</t>
+    <t>commercialhealthplan</t>
   </si>
   <si>
     <t>noinsurance</t>
@@ -186,7 +186,7 @@
     <t>neversmoker</t>
   </si>
   <si>
-    <t>academicmedicalce~r</t>
+    <t>academicmedicalcenter</t>
   </si>
   <si>
     <t>kidney_bool</t>
@@ -195,10 +195,10 @@
     <t>liver_bool</t>
   </si>
   <si>
-    <t>connective_tissue~l</t>
+    <t>connective_tissue_bool</t>
   </si>
   <si>
-    <t>interstitiallungd~e</t>
+    <t>interstitiallungdisease</t>
   </si>
   <si>
     <t>diabetes</t>
@@ -213,28 +213,28 @@
     <t>othercnsmetastases</t>
   </si>
   <si>
-    <t>digestivesystemme~s</t>
+    <t>digestivesystemmetastases</t>
   </si>
   <si>
     <t>adrenalmetastases</t>
   </si>
   <si>
-    <t>unspecifiedmetast~s</t>
+    <t>unspecifiedmetastases</t>
   </si>
   <si>
-    <t>antiinfectiveusep~t</t>
+    <t>antiinfectiveusepriortotreatment</t>
   </si>
   <si>
-    <t>glucocorticoiduse~n</t>
+    <t>glucocorticoidusepriortotreatmen</t>
   </si>
   <si>
-    <t>clinicalstudydrug~d</t>
+    <t>clinicalstudydrugused</t>
   </si>
   <si>
     <t>bevacizumabused</t>
   </si>
   <si>
-    <t>threeormorechemot~s</t>
+    <t>threeormorechemotherapydrugs</t>
   </si>
   <si>
     <t>pdl1reported</t>

--- a/progression_odds_all.xlsx
+++ b/progression_odds_all.xlsx
@@ -10230,22 +10230,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="25">
-        <v>1.357753</v>
+        <v>1.1886890000000001</v>
       </c>
       <c r="C2" s="26">
-        <v>0.22224630000000001</v>
+        <v>0.72803110000000004</v>
       </c>
       <c r="D2" s="27">
-        <v>1.8700000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E2" s="28">
-        <v>0.062</v>
+        <v>0.77800000000000002</v>
       </c>
       <c r="F2" s="29">
-        <v>0.9851221</v>
+        <v>0.35787950000000002</v>
       </c>
       <c r="G2" s="30">
-        <v>1.8713329999999999</v>
+        <v>3.948207</v>
       </c>
     </row>
     <row r="3">
@@ -10253,22 +10253,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="33">
-        <v>1.253906</v>
+        <v>0.94679979999999997</v>
       </c>
       <c r="C3" s="34">
-        <v>0.1998722</v>
+        <v>0.048501900000000001</v>
       </c>
       <c r="D3" s="35">
-        <v>1.4199999999999999</v>
+        <v>-1.0700000000000001</v>
       </c>
       <c r="E3" s="36">
-        <v>0.156</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="F3" s="37">
-        <v>0.91745290000000002</v>
+        <v>0.85635430000000001</v>
       </c>
       <c r="G3" s="38">
-        <v>1.7137450000000001</v>
+        <v>1.0467979999999999</v>
       </c>
     </row>
     <row r="4">
@@ -10276,22 +10276,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="41">
-        <v>2.1276600000000001</v>
+        <v>1.605864</v>
       </c>
       <c r="C4" s="42">
-        <v>0.36961090000000002</v>
+        <v>0.13743710000000001</v>
       </c>
       <c r="D4" s="43">
-        <v>4.3499999999999996</v>
+        <v>5.5300000000000002</v>
       </c>
       <c r="E4" s="44">
         <v>0</v>
       </c>
       <c r="F4" s="45">
-        <v>1.5136799999999999</v>
+        <v>1.3578730000000001</v>
       </c>
       <c r="G4" s="46">
-        <v>2.9906839999999999</v>
+        <v>1.899146</v>
       </c>
     </row>
     <row r="5">
@@ -10299,22 +10299,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="49">
-        <v>1.1742509999999999</v>
+        <v>0.90028490000000005</v>
       </c>
       <c r="C5" s="50">
-        <v>0.18542449999999999</v>
+        <v>0.060673600000000001</v>
       </c>
       <c r="D5" s="51">
-        <v>1.02</v>
+        <v>-1.5600000000000001</v>
       </c>
       <c r="E5" s="52">
-        <v>0.309</v>
+        <v>0.11899999999999999</v>
       </c>
       <c r="F5" s="53">
-        <v>0.8616857</v>
+        <v>0.78888610000000003</v>
       </c>
       <c r="G5" s="54">
-        <v>1.600196</v>
+        <v>1.027414</v>
       </c>
     </row>
     <row r="6">
@@ -10322,22 +10322,22 @@
         <v>11</v>
       </c>
       <c r="B6" s="57">
-        <v>1.1191800000000001</v>
+        <v>0.70913009999999999</v>
       </c>
       <c r="C6" s="58">
-        <v>0.18230270000000001</v>
+        <v>0.43342360000000002</v>
       </c>
       <c r="D6" s="59">
-        <v>0.68999999999999995</v>
+        <v>-0.56000000000000005</v>
       </c>
       <c r="E6" s="60">
-        <v>0.48899999999999999</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="F6" s="61">
-        <v>0.8132952</v>
+        <v>0.21402650000000001</v>
       </c>
       <c r="G6" s="62">
-        <v>1.5401100000000001</v>
+        <v>2.349548</v>
       </c>
     </row>
     <row r="7">
@@ -10345,22 +10345,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="65">
-        <v>1.2338610000000001</v>
+        <v>0.93782460000000001</v>
       </c>
       <c r="C7" s="66">
-        <v>0.38278040000000002</v>
+        <v>0.25536029999999999</v>
       </c>
       <c r="D7" s="67">
-        <v>0.68000000000000005</v>
+        <v>-0.23999999999999999</v>
       </c>
       <c r="E7" s="68">
-        <v>0.498</v>
+        <v>0.81399999999999995</v>
       </c>
       <c r="F7" s="69">
-        <v>0.67173519999999998</v>
+        <v>0.54998130000000001</v>
       </c>
       <c r="G7" s="70">
-        <v>2.2663880000000001</v>
+        <v>1.599173</v>
       </c>
     </row>
     <row r="8">
@@ -10368,22 +10368,22 @@
         <v>13</v>
       </c>
       <c r="B8" s="73">
-        <v>1.0313209999999999</v>
+        <v>0.82479139999999995</v>
       </c>
       <c r="C8" s="74">
-        <v>0.77493939999999995</v>
+        <v>0.60531800000000002</v>
       </c>
       <c r="D8" s="75">
-        <v>0.040000000000000001</v>
+        <v>-0.26000000000000001</v>
       </c>
       <c r="E8" s="76">
-        <v>0.96699999999999997</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="F8" s="77">
-        <v>0.23648150000000001</v>
+        <v>0.1957238</v>
       </c>
       <c r="G8" s="78">
-        <v>4.4977020000000003</v>
+        <v>3.4757189999999998</v>
       </c>
     </row>
     <row r="9">
@@ -10391,22 +10391,22 @@
         <v>14</v>
       </c>
       <c r="B9" s="81">
-        <v>2.1911230000000002</v>
+        <v>1.6323700000000001</v>
       </c>
       <c r="C9" s="82">
-        <v>1.560478</v>
+        <v>1.133365</v>
       </c>
       <c r="D9" s="83">
-        <v>1.1000000000000001</v>
+        <v>0.70999999999999997</v>
       </c>
       <c r="E9" s="84">
-        <v>0.27100000000000002</v>
+        <v>0.47999999999999998</v>
       </c>
       <c r="F9" s="85">
-        <v>0.54257040000000001</v>
+        <v>0.41862349999999998</v>
       </c>
       <c r="G9" s="86">
-        <v>8.8486550000000008</v>
+        <v>6.365221</v>
       </c>
     </row>
     <row r="10">
@@ -10414,22 +10414,22 @@
         <v>15</v>
       </c>
       <c r="B10" s="89">
-        <v>1.014059</v>
+        <v>0.76480170000000003</v>
       </c>
       <c r="C10" s="90">
-        <v>0.25553360000000003</v>
+        <v>0.153976</v>
       </c>
       <c r="D10" s="91">
-        <v>0.059999999999999998</v>
+        <v>-1.3300000000000001</v>
       </c>
       <c r="E10" s="92">
-        <v>0.95599999999999996</v>
+        <v>0.183</v>
       </c>
       <c r="F10" s="93">
-        <v>0.61882579999999998</v>
+        <v>0.51544000000000001</v>
       </c>
       <c r="G10" s="94">
-        <v>1.6617219999999999</v>
+        <v>1.134801</v>
       </c>
     </row>
     <row r="11">
@@ -10437,22 +10437,22 @@
         <v>16</v>
       </c>
       <c r="B11" s="97">
-        <v>0.63879359999999996</v>
+        <v>0.48209380000000002</v>
       </c>
       <c r="C11" s="98">
-        <v>0.28717300000000001</v>
+        <v>0.20411380000000001</v>
       </c>
       <c r="D11" s="99">
-        <v>-1</v>
+        <v>-1.72</v>
       </c>
       <c r="E11" s="100">
-        <v>0.31900000000000001</v>
+        <v>0.085000000000000006</v>
       </c>
       <c r="F11" s="101">
-        <v>0.26466620000000002</v>
+        <v>0.21025240000000001</v>
       </c>
       <c r="G11" s="102">
-        <v>1.5417810000000001</v>
+        <v>1.105407</v>
       </c>
     </row>
     <row r="12">
@@ -10506,10 +10506,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="121">
-        <v>0.55623789999999995</v>
+        <v>0.5561564</v>
       </c>
       <c r="C14" s="122">
-        <v>0.063396599999999997</v>
+        <v>0.063395099999999996</v>
       </c>
       <c r="D14" s="123">
         <v>-5.1500000000000004</v>
@@ -10518,10 +10518,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="125">
-        <v>0.44488299999999997</v>
+        <v>0.44480570000000003</v>
       </c>
       <c r="G14" s="126">
-        <v>0.69546509999999995</v>
+        <v>0.69538219999999995</v>
       </c>
     </row>
     <row r="15">
@@ -10529,22 +10529,22 @@
         <v>19</v>
       </c>
       <c r="B15" s="129">
-        <v>1.3255269999999999</v>
+        <v>1.049205</v>
       </c>
       <c r="C15" s="130">
-        <v>0.87381690000000001</v>
+        <v>0.68123420000000001</v>
       </c>
       <c r="D15" s="131">
-        <v>0.42999999999999999</v>
+        <v>0.070000000000000007</v>
       </c>
       <c r="E15" s="132">
-        <v>0.66900000000000004</v>
+        <v>0.94099999999999995</v>
       </c>
       <c r="F15" s="133">
-        <v>0.36413129999999999</v>
+        <v>0.29389159999999998</v>
       </c>
       <c r="G15" s="134">
-        <v>4.8252470000000001</v>
+        <v>3.7457060000000002</v>
       </c>
     </row>
     <row r="16">
@@ -10552,22 +10552,22 @@
         <v>20</v>
       </c>
       <c r="B16" s="137">
-        <v>0.37987500000000002</v>
+        <v>0.28876669999999999</v>
       </c>
       <c r="C16" s="138">
-        <v>0.079771599999999998</v>
+        <v>0.043010399999999997</v>
       </c>
       <c r="D16" s="139">
-        <v>-4.6100000000000003</v>
+        <v>-8.3399999999999999</v>
       </c>
       <c r="E16" s="140">
         <v>0</v>
       </c>
       <c r="F16" s="141">
-        <v>0.25170569999999998</v>
+        <v>0.2156576</v>
       </c>
       <c r="G16" s="142">
-        <v>0.57330840000000005</v>
+        <v>0.38666010000000001</v>
       </c>
     </row>
     <row r="17">
@@ -10621,22 +10621,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="161">
-        <v>0.81782580000000005</v>
+        <v>0.81664490000000001</v>
       </c>
       <c r="C19" s="162">
-        <v>0.052415499999999997</v>
+        <v>0.052333999999999999</v>
       </c>
       <c r="D19" s="163">
-        <v>-3.1400000000000001</v>
+        <v>-3.1600000000000001</v>
       </c>
       <c r="E19" s="164">
         <v>0.002</v>
       </c>
       <c r="F19" s="165">
-        <v>0.72128389999999998</v>
+        <v>0.72025249999999996</v>
       </c>
       <c r="G19" s="166">
-        <v>0.92728960000000005</v>
+        <v>0.92593769999999998</v>
       </c>
     </row>
     <row r="20">
@@ -10644,22 +10644,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="169">
-        <v>1.6772069999999999</v>
+        <v>1.27603</v>
       </c>
       <c r="C20" s="170">
-        <v>0.30474289999999998</v>
+        <v>0.135403</v>
       </c>
       <c r="D20" s="171">
-        <v>2.8500000000000001</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E20" s="172">
-        <v>0.0040000000000000001</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="F20" s="173">
-        <v>1.174698</v>
+        <v>1.036424</v>
       </c>
       <c r="G20" s="174">
-        <v>2.3946779999999999</v>
+        <v>1.571029</v>
       </c>
     </row>
     <row r="21">
@@ -10667,22 +10667,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="177">
-        <v>0.61454399999999998</v>
+        <v>0.46695419999999999</v>
       </c>
       <c r="C21" s="178">
-        <v>0.097524899999999998</v>
+        <v>0.027012000000000001</v>
       </c>
       <c r="D21" s="179">
-        <v>-3.0699999999999999</v>
+        <v>-13.16</v>
       </c>
       <c r="E21" s="180">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="F21" s="181">
-        <v>0.45026860000000002</v>
+        <v>0.41690260000000001</v>
       </c>
       <c r="G21" s="182">
-        <v>0.83875330000000003</v>
+        <v>0.5230148</v>
       </c>
     </row>
     <row r="22">
@@ -10736,22 +10736,22 @@
         <v>18</v>
       </c>
       <c r="B24" s="201">
-        <v>0.96795949999999997</v>
+        <v>0.96339940000000002</v>
       </c>
       <c r="C24" s="202">
-        <v>0.21150189999999999</v>
+        <v>0.210422</v>
       </c>
       <c r="D24" s="203">
-        <v>-0.15</v>
+        <v>-0.17000000000000001</v>
       </c>
       <c r="E24" s="204">
-        <v>0.88200000000000001</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="F24" s="205">
-        <v>0.63076449999999995</v>
+        <v>0.6278996</v>
       </c>
       <c r="G24" s="206">
-        <v>1.4854130000000001</v>
+        <v>1.478164</v>
       </c>
     </row>
     <row r="25">
@@ -10759,22 +10759,22 @@
         <v>19</v>
       </c>
       <c r="B25" s="209">
-        <v>1.535342</v>
+        <v>1.171556</v>
       </c>
       <c r="C25" s="210">
-        <v>0.3247602</v>
+        <v>0.17995449999999999</v>
       </c>
       <c r="D25" s="211">
-        <v>2.0299999999999998</v>
+        <v>1.03</v>
       </c>
       <c r="E25" s="212">
-        <v>0.042999999999999997</v>
+        <v>0.30299999999999999</v>
       </c>
       <c r="F25" s="213">
-        <v>1.014276</v>
+        <v>0.86699400000000004</v>
       </c>
       <c r="G25" s="214">
-        <v>2.3240949999999998</v>
+        <v>1.583107</v>
       </c>
     </row>
     <row r="26">
@@ -10782,22 +10782,22 @@
         <v>20</v>
       </c>
       <c r="B26" s="217">
-        <v>1.0342929999999999</v>
+        <v>0.79288069999999999</v>
       </c>
       <c r="C26" s="218">
-        <v>0.27796559999999998</v>
+        <v>0.17991550000000001</v>
       </c>
       <c r="D26" s="219">
-        <v>0.13</v>
+        <v>-1.02</v>
       </c>
       <c r="E26" s="220">
-        <v>0.90000000000000002</v>
+        <v>0.306</v>
       </c>
       <c r="F26" s="221">
-        <v>0.6107783</v>
+        <v>0.50822789999999995</v>
       </c>
       <c r="G26" s="222">
-        <v>1.7514730000000001</v>
+        <v>1.236964</v>
       </c>
     </row>
     <row r="27">
@@ -10828,22 +10828,22 @@
         <v>23</v>
       </c>
       <c r="B28" s="233">
-        <v>0.9788943</v>
+        <v>0.97821290000000005</v>
       </c>
       <c r="C28" s="234">
-        <v>0.078322900000000001</v>
+        <v>0.078256099999999995</v>
       </c>
       <c r="D28" s="235">
-        <v>-0.27000000000000002</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="E28" s="236">
-        <v>0.79000000000000004</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="F28" s="237">
-        <v>0.83681559999999999</v>
+        <v>0.83625369999999999</v>
       </c>
       <c r="G28" s="238">
-        <v>1.1450959999999999</v>
+        <v>1.1442699999999999</v>
       </c>
     </row>
     <row r="29">
@@ -10851,22 +10851,22 @@
         <v>24</v>
       </c>
       <c r="B29" s="241">
-        <v>1.1550199999999999</v>
+        <v>1.1559729999999999</v>
       </c>
       <c r="C29" s="242">
-        <v>0.045443999999999998</v>
+        <v>0.045477499999999997</v>
       </c>
       <c r="D29" s="243">
-        <v>3.6600000000000001</v>
+        <v>3.6800000000000002</v>
       </c>
       <c r="E29" s="244">
         <v>0</v>
       </c>
       <c r="F29" s="245">
-        <v>1.069299</v>
+        <v>1.0701879999999999</v>
       </c>
       <c r="G29" s="246">
-        <v>1.2476130000000001</v>
+        <v>1.2486330000000001</v>
       </c>
     </row>
     <row r="30">
@@ -10874,22 +10874,22 @@
         <v>25</v>
       </c>
       <c r="B30" s="249">
-        <v>0.46026309999999998</v>
+        <v>0.46004050000000002</v>
       </c>
       <c r="C30" s="250">
-        <v>0.019343699999999998</v>
+        <v>0.019332499999999999</v>
       </c>
       <c r="D30" s="251">
-        <v>-18.460000000000001</v>
+        <v>-18.48</v>
       </c>
       <c r="E30" s="252">
         <v>0</v>
       </c>
       <c r="F30" s="253">
-        <v>0.42386970000000002</v>
+        <v>0.42366789999999999</v>
       </c>
       <c r="G30" s="254">
-        <v>0.49978129999999998</v>
+        <v>0.49953570000000003</v>
       </c>
     </row>
     <row r="31">
@@ -10897,22 +10897,22 @@
         <v>26</v>
       </c>
       <c r="B31" s="257">
-        <v>0.73555570000000003</v>
+        <v>0.73609559999999996</v>
       </c>
       <c r="C31" s="258">
-        <v>0.0267435</v>
+        <v>0.026760200000000001</v>
       </c>
       <c r="D31" s="259">
-        <v>-8.4499999999999993</v>
+        <v>-8.4299999999999997</v>
       </c>
       <c r="E31" s="260">
         <v>0</v>
       </c>
       <c r="F31" s="261">
-        <v>0.6849634</v>
+        <v>0.68547150000000001</v>
       </c>
       <c r="G31" s="262">
-        <v>0.7898847</v>
+        <v>0.79045829999999995</v>
       </c>
     </row>
     <row r="32">
@@ -10920,22 +10920,22 @@
         <v>27</v>
       </c>
       <c r="B32" s="265">
-        <v>1.0949180000000001</v>
+        <v>1.0959410000000001</v>
       </c>
       <c r="C32" s="266">
-        <v>0.043825700000000002</v>
+        <v>0.043862100000000001</v>
       </c>
       <c r="D32" s="267">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="E32" s="268">
-        <v>0.023</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="F32" s="269">
-        <v>1.0123040000000001</v>
+        <v>1.013258</v>
       </c>
       <c r="G32" s="270">
-        <v>1.184274</v>
+        <v>1.185371</v>
       </c>
     </row>
     <row r="33">
@@ -10943,22 +10943,22 @@
         <v>28</v>
       </c>
       <c r="B33" s="273">
-        <v>1.451665</v>
+        <v>1.453908</v>
       </c>
       <c r="C33" s="274">
-        <v>0.069461300000000004</v>
+        <v>0.069554099999999994</v>
       </c>
       <c r="D33" s="275">
-        <v>7.79</v>
+        <v>7.8200000000000003</v>
       </c>
       <c r="E33" s="276">
         <v>0</v>
       </c>
       <c r="F33" s="277">
-        <v>1.321712</v>
+        <v>1.32378</v>
       </c>
       <c r="G33" s="278">
-        <v>1.594395</v>
+        <v>1.596827</v>
       </c>
     </row>
     <row r="34">
@@ -10966,22 +10966,22 @@
         <v>29</v>
       </c>
       <c r="B34" s="281">
-        <v>1.432834</v>
+        <v>1.4377819999999999</v>
       </c>
       <c r="C34" s="282">
-        <v>0.1526103</v>
+        <v>0.1531209</v>
       </c>
       <c r="D34" s="283">
-        <v>3.3799999999999999</v>
+        <v>3.4100000000000001</v>
       </c>
       <c r="E34" s="284">
         <v>0.001</v>
       </c>
       <c r="F34" s="285">
-        <v>1.1628799999999999</v>
+        <v>1.166922</v>
       </c>
       <c r="G34" s="286">
-        <v>1.7654559999999999</v>
+        <v>1.771512</v>
       </c>
     </row>
     <row r="35">
@@ -10989,22 +10989,22 @@
         <v>30</v>
       </c>
       <c r="B35" s="289">
-        <v>0.97140219999999999</v>
+        <v>0.97263569999999999</v>
       </c>
       <c r="C35" s="290">
-        <v>0.064196500000000004</v>
+        <v>0.064271499999999995</v>
       </c>
       <c r="D35" s="291">
-        <v>-0.44</v>
+        <v>-0.41999999999999999</v>
       </c>
       <c r="E35" s="292">
-        <v>0.66100000000000003</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="F35" s="293">
-        <v>0.85338749999999997</v>
+        <v>0.85448230000000003</v>
       </c>
       <c r="G35" s="294">
-        <v>1.105737</v>
+        <v>1.107127</v>
       </c>
     </row>
     <row r="36">
@@ -11012,10 +11012,10 @@
         <v>31</v>
       </c>
       <c r="B36" s="297">
-        <v>0.82194829999999997</v>
+        <v>0.82177500000000003</v>
       </c>
       <c r="C36" s="298">
-        <v>0.0515112</v>
+        <v>0.051496500000000001</v>
       </c>
       <c r="D36" s="299">
         <v>-3.1299999999999999</v>
@@ -11024,10 +11024,10 @@
         <v>0.002</v>
       </c>
       <c r="F36" s="301">
-        <v>0.72694239999999999</v>
+        <v>0.72679579999999999</v>
       </c>
       <c r="G36" s="302">
-        <v>0.92937060000000005</v>
+        <v>0.9291663</v>
       </c>
     </row>
     <row r="37">
@@ -11035,22 +11035,22 @@
         <v>32</v>
       </c>
       <c r="B37" s="305">
-        <v>0.54424380000000006</v>
+        <v>0.54847780000000002</v>
       </c>
       <c r="C37" s="306">
-        <v>0.030286</v>
+        <v>0.0304373</v>
       </c>
       <c r="D37" s="307">
-        <v>-10.93</v>
+        <v>-10.82</v>
       </c>
       <c r="E37" s="308">
         <v>0</v>
       </c>
       <c r="F37" s="309">
-        <v>0.48800690000000002</v>
+        <v>0.49195159999999999</v>
       </c>
       <c r="G37" s="310">
-        <v>0.60696130000000004</v>
+        <v>0.61149900000000001</v>
       </c>
     </row>
     <row r="38">
@@ -11058,22 +11058,22 @@
         <v>33</v>
       </c>
       <c r="B38" s="313">
-        <v>0.86982150000000003</v>
+        <v>0.86998880000000001</v>
       </c>
       <c r="C38" s="314">
-        <v>0.060025799999999997</v>
+        <v>0.060043600000000003</v>
       </c>
       <c r="D38" s="315">
         <v>-2.02</v>
       </c>
       <c r="E38" s="316">
-        <v>0.042999999999999997</v>
+        <v>0.043999999999999998</v>
       </c>
       <c r="F38" s="317">
-        <v>0.75978259999999998</v>
+        <v>0.75991790000000004</v>
       </c>
       <c r="G38" s="318">
-        <v>0.99579740000000005</v>
+        <v>0.99600310000000003</v>
       </c>
     </row>
     <row r="39">
@@ -11081,22 +11081,22 @@
         <v>34</v>
       </c>
       <c r="B39" s="321">
-        <v>1.0085120000000001</v>
+        <v>1.0078290000000001</v>
       </c>
       <c r="C39" s="322">
-        <v>0.0064542999999999996</v>
+        <v>0.0064399000000000001</v>
       </c>
       <c r="D39" s="323">
-        <v>1.3200000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="E39" s="324">
-        <v>0.185</v>
+        <v>0.222</v>
       </c>
       <c r="F39" s="325">
-        <v>0.99594070000000001</v>
+        <v>0.99528539999999999</v>
       </c>
       <c r="G39" s="326">
-        <v>1.021242</v>
+        <v>1.0205299999999999</v>
       </c>
     </row>
     <row r="40">
@@ -11104,22 +11104,22 @@
         <v>35</v>
       </c>
       <c r="B40" s="329">
-        <v>0.46828930000000002</v>
+        <v>0.46862959999999998</v>
       </c>
       <c r="C40" s="330">
-        <v>0.043027799999999998</v>
+        <v>0.043056900000000002</v>
       </c>
       <c r="D40" s="331">
-        <v>-8.2599999999999998</v>
+        <v>-8.25</v>
       </c>
       <c r="E40" s="332">
         <v>0</v>
       </c>
       <c r="F40" s="333">
-        <v>0.39111390000000001</v>
+        <v>0.39140180000000002</v>
       </c>
       <c r="G40" s="334">
-        <v>0.56069310000000006</v>
+        <v>0.56109529999999996</v>
       </c>
     </row>
     <row r="41">
@@ -11127,10 +11127,10 @@
         <v>36</v>
       </c>
       <c r="B41" s="337">
-        <v>0.85472570000000003</v>
+        <v>0.85479859999999997</v>
       </c>
       <c r="C41" s="338">
-        <v>0.0389959</v>
+        <v>0.038996799999999998</v>
       </c>
       <c r="D41" s="339">
         <v>-3.44</v>
@@ -11139,10 +11139,10 @@
         <v>0.001</v>
       </c>
       <c r="F41" s="341">
-        <v>0.78161270000000005</v>
+        <v>0.78168380000000004</v>
       </c>
       <c r="G41" s="342">
-        <v>0.93467769999999995</v>
+        <v>0.93475229999999998</v>
       </c>
     </row>
     <row r="42">
@@ -11150,22 +11150,22 @@
         <v>37</v>
       </c>
       <c r="B42" s="345">
-        <v>0.86567079999999996</v>
+        <v>0.86625640000000004</v>
       </c>
       <c r="C42" s="346">
-        <v>0.072383100000000006</v>
+        <v>0.072420899999999996</v>
       </c>
       <c r="D42" s="347">
-        <v>-1.73</v>
+        <v>-1.72</v>
       </c>
       <c r="E42" s="348">
-        <v>0.084000000000000005</v>
+        <v>0.085999999999999993</v>
       </c>
       <c r="F42" s="349">
-        <v>0.73481770000000002</v>
+        <v>0.73533320000000002</v>
       </c>
       <c r="G42" s="350">
-        <v>1.0198259999999999</v>
+        <v>1.0204899999999999</v>
       </c>
     </row>
     <row r="43">
@@ -11173,22 +11173,22 @@
         <v>38</v>
       </c>
       <c r="B43" s="353">
-        <v>0.79498020000000003</v>
+        <v>0.79460399999999998</v>
       </c>
       <c r="C43" s="354">
-        <v>0.047374800000000002</v>
+        <v>0.047350999999999997</v>
       </c>
       <c r="D43" s="355">
-        <v>-3.8500000000000001</v>
+        <v>-3.8599999999999999</v>
       </c>
       <c r="E43" s="356">
         <v>0</v>
       </c>
       <c r="F43" s="357">
-        <v>0.7073448</v>
+        <v>0.70701250000000004</v>
       </c>
       <c r="G43" s="358">
-        <v>0.89347299999999996</v>
+        <v>0.89304729999999999</v>
       </c>
     </row>
     <row r="44">
@@ -11196,10 +11196,10 @@
         <v>39</v>
       </c>
       <c r="B44" s="361">
-        <v>0.86984159999999999</v>
+        <v>0.86954600000000004</v>
       </c>
       <c r="C44" s="362">
-        <v>0.050432900000000003</v>
+        <v>0.050413399999999997</v>
       </c>
       <c r="D44" s="363">
         <v>-2.4100000000000001</v>
@@ -11208,10 +11208,10 @@
         <v>0.016</v>
       </c>
       <c r="F44" s="365">
-        <v>0.7764044</v>
+        <v>0.77614470000000002</v>
       </c>
       <c r="G44" s="366">
-        <v>0.97452349999999999</v>
+        <v>0.97418720000000003</v>
       </c>
     </row>
     <row r="45">
@@ -11219,22 +11219,22 @@
         <v>40</v>
       </c>
       <c r="B45" s="369">
-        <v>0.77263300000000001</v>
+        <v>0.7707387</v>
       </c>
       <c r="C45" s="370">
-        <v>0.26068390000000002</v>
+        <v>0.26000640000000003</v>
       </c>
       <c r="D45" s="371">
-        <v>-0.76000000000000001</v>
+        <v>-0.77000000000000002</v>
       </c>
       <c r="E45" s="372">
-        <v>0.44500000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="F45" s="373">
-        <v>0.3988234</v>
+        <v>0.39788440000000003</v>
       </c>
       <c r="G45" s="374">
-        <v>1.496807</v>
+        <v>1.4929920000000001</v>
       </c>
     </row>
     <row r="46">
@@ -11242,22 +11242,22 @@
         <v>41</v>
       </c>
       <c r="B46" s="377">
-        <v>1.153386</v>
+        <v>1.1536090000000001</v>
       </c>
       <c r="C46" s="378">
-        <v>0.028703099999999999</v>
+        <v>0.028707099999999999</v>
       </c>
       <c r="D46" s="379">
-        <v>5.7300000000000004</v>
+        <v>5.7400000000000002</v>
       </c>
       <c r="E46" s="380">
         <v>0</v>
       </c>
       <c r="F46" s="381">
-        <v>1.098479</v>
+        <v>1.0986940000000001</v>
       </c>
       <c r="G46" s="382">
-        <v>1.2110380000000001</v>
+        <v>1.211268</v>
       </c>
     </row>
     <row r="47">
@@ -11265,22 +11265,22 @@
         <v>42</v>
       </c>
       <c r="B47" s="385">
-        <v>0.9694874</v>
+        <v>0.9690183</v>
       </c>
       <c r="C47" s="386">
-        <v>0.0146201</v>
+        <v>0.0146102</v>
       </c>
       <c r="D47" s="387">
-        <v>-2.0499999999999998</v>
+        <v>-2.0899999999999999</v>
       </c>
       <c r="E47" s="388">
-        <v>0.040000000000000001</v>
+        <v>0.036999999999999998</v>
       </c>
       <c r="F47" s="389">
-        <v>0.94125190000000003</v>
+        <v>0.94080180000000002</v>
       </c>
       <c r="G47" s="390">
-        <v>0.99856990000000001</v>
+        <v>0.9980812</v>
       </c>
     </row>
     <row r="48">
@@ -11288,22 +11288,22 @@
         <v>43</v>
       </c>
       <c r="B48" s="393">
-        <v>0.76144999999999996</v>
+        <v>0.76178140000000005</v>
       </c>
       <c r="C48" s="394">
-        <v>0.027975300000000002</v>
+        <v>0.0279879</v>
       </c>
       <c r="D48" s="395">
-        <v>-7.4199999999999999</v>
+        <v>-7.4100000000000001</v>
       </c>
       <c r="E48" s="396">
         <v>0</v>
       </c>
       <c r="F48" s="397">
-        <v>0.70854709999999999</v>
+        <v>0.7088546</v>
       </c>
       <c r="G48" s="398">
-        <v>0.81830290000000006</v>
+        <v>0.81866000000000005</v>
       </c>
     </row>
     <row r="49">
@@ -11311,22 +11311,22 @@
         <v>44</v>
       </c>
       <c r="B49" s="401">
-        <v>0.91014459999999997</v>
+        <v>0.9098733</v>
       </c>
       <c r="C49" s="402">
-        <v>0.047829200000000002</v>
+        <v>0.047814099999999998</v>
       </c>
       <c r="D49" s="403">
-        <v>-1.79</v>
+        <v>-1.8</v>
       </c>
       <c r="E49" s="404">
-        <v>0.072999999999999996</v>
+        <v>0.071999999999999995</v>
       </c>
       <c r="F49" s="405">
-        <v>0.8210672</v>
+        <v>0.82082390000000005</v>
       </c>
       <c r="G49" s="406">
-        <v>1.008886</v>
+        <v>1.008583</v>
       </c>
     </row>
     <row r="50">
@@ -11334,22 +11334,22 @@
         <v>45</v>
       </c>
       <c r="B50" s="409">
-        <v>0.84242360000000005</v>
+        <v>0.84295730000000002</v>
       </c>
       <c r="C50" s="410">
-        <v>0.022545200000000001</v>
+        <v>0.022556400000000001</v>
       </c>
       <c r="D50" s="411">
-        <v>-6.4100000000000001</v>
+        <v>-6.3799999999999999</v>
       </c>
       <c r="E50" s="412">
         <v>0</v>
       </c>
       <c r="F50" s="413">
-        <v>0.79937480000000005</v>
+        <v>0.79988680000000001</v>
       </c>
       <c r="G50" s="414">
-        <v>0.88779079999999999</v>
+        <v>0.888347</v>
       </c>
     </row>
     <row r="51">
@@ -11357,10 +11357,10 @@
         <v>46</v>
       </c>
       <c r="B51" s="417">
-        <v>0.78679299999999997</v>
+        <v>0.7867497</v>
       </c>
       <c r="C51" s="418">
-        <v>0.051798299999999999</v>
+        <v>0.051803500000000002</v>
       </c>
       <c r="D51" s="419">
         <v>-3.6400000000000001</v>
@@ -11369,10 +11369,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="421">
-        <v>0.69154720000000003</v>
+        <v>0.69149539999999998</v>
       </c>
       <c r="G51" s="422">
-        <v>0.89515690000000003</v>
+        <v>0.89512539999999996</v>
       </c>
     </row>
     <row r="52">
@@ -11380,22 +11380,22 @@
         <v>47</v>
       </c>
       <c r="B52" s="425">
-        <v>0.9147092</v>
+        <v>0.91430699999999998</v>
       </c>
       <c r="C52" s="426">
-        <v>0.0472746</v>
+        <v>0.0472536</v>
       </c>
       <c r="D52" s="427">
-        <v>-1.72</v>
+        <v>-1.73</v>
       </c>
       <c r="E52" s="428">
-        <v>0.085000000000000006</v>
+        <v>0.083000000000000004</v>
       </c>
       <c r="F52" s="429">
-        <v>0.82659110000000002</v>
+        <v>0.82622790000000002</v>
       </c>
       <c r="G52" s="430">
-        <v>1.012221</v>
+        <v>1.011776</v>
       </c>
     </row>
     <row r="53">
@@ -11403,22 +11403,22 @@
         <v>48</v>
       </c>
       <c r="B53" s="433">
-        <v>0.92288820000000005</v>
+        <v>0.92320159999999996</v>
       </c>
       <c r="C53" s="434">
-        <v>0.023492900000000001</v>
+        <v>0.0235</v>
       </c>
       <c r="D53" s="435">
-        <v>-3.1499999999999999</v>
+        <v>-3.1400000000000001</v>
       </c>
       <c r="E53" s="436">
         <v>0.002</v>
       </c>
       <c r="F53" s="437">
-        <v>0.8779728</v>
+        <v>0.87827250000000001</v>
       </c>
       <c r="G53" s="438">
-        <v>0.97010130000000006</v>
+        <v>0.97042910000000004</v>
       </c>
     </row>
     <row r="54">
@@ -11426,22 +11426,22 @@
         <v>49</v>
       </c>
       <c r="B54" s="441">
-        <v>0.81285079999999999</v>
+        <v>0.81269049999999998</v>
       </c>
       <c r="C54" s="442">
-        <v>0.021420000000000002</v>
+        <v>0.021414800000000001</v>
       </c>
       <c r="D54" s="443">
-        <v>-7.8600000000000003</v>
+        <v>-7.8700000000000001</v>
       </c>
       <c r="E54" s="444">
         <v>0</v>
       </c>
       <c r="F54" s="445">
-        <v>0.77193409999999996</v>
+        <v>0.77178369999999996</v>
       </c>
       <c r="G54" s="446">
-        <v>0.85593629999999998</v>
+        <v>0.85576549999999996</v>
       </c>
     </row>
     <row r="55">
@@ -11449,22 +11449,22 @@
         <v>50</v>
       </c>
       <c r="B55" s="449">
-        <v>0.77340529999999996</v>
+        <v>0.77146369999999998</v>
       </c>
       <c r="C55" s="450">
-        <v>1.1001270000000001</v>
+        <v>1.0973809999999999</v>
       </c>
       <c r="D55" s="451">
         <v>-0.17999999999999999</v>
       </c>
       <c r="E55" s="452">
-        <v>0.85699999999999999</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="F55" s="453">
-        <v>0.047601400000000002</v>
+        <v>0.047480000000000001</v>
       </c>
       <c r="G55" s="454">
-        <v>12.56593</v>
+        <v>12.534890000000001</v>
       </c>
     </row>
     <row r="56">
@@ -11472,22 +11472,22 @@
         <v>51</v>
       </c>
       <c r="B56" s="457">
-        <v>0.72609999999999997</v>
+        <v>0.72507219999999995</v>
       </c>
       <c r="C56" s="458">
-        <v>0.068958000000000005</v>
+        <v>0.068854299999999993</v>
       </c>
       <c r="D56" s="459">
-        <v>-3.3700000000000001</v>
+        <v>-3.3900000000000001</v>
       </c>
       <c r="E56" s="460">
         <v>0.001</v>
       </c>
       <c r="F56" s="461">
-        <v>0.60277809999999998</v>
+        <v>0.60193470000000004</v>
       </c>
       <c r="G56" s="462">
-        <v>0.87465210000000004</v>
+        <v>0.87339979999999995</v>
       </c>
     </row>
     <row r="57">
@@ -11495,22 +11495,22 @@
         <v>52</v>
       </c>
       <c r="B57" s="465">
-        <v>0.88618260000000004</v>
+        <v>0.88655709999999999</v>
       </c>
       <c r="C57" s="466">
-        <v>0.089353799999999997</v>
+        <v>0.089384400000000003</v>
       </c>
       <c r="D57" s="467">
-        <v>-1.2</v>
+        <v>-1.19</v>
       </c>
       <c r="E57" s="468">
-        <v>0.23100000000000001</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="F57" s="469">
-        <v>0.72727149999999996</v>
+        <v>0.72759039999999997</v>
       </c>
       <c r="G57" s="470">
-        <v>1.0798160000000001</v>
+        <v>1.0802560000000001</v>
       </c>
     </row>
     <row r="58">
@@ -11518,22 +11518,22 @@
         <v>53</v>
       </c>
       <c r="B58" s="473">
-        <v>0.69304710000000003</v>
+        <v>0.69201299999999999</v>
       </c>
       <c r="C58" s="474">
-        <v>0.062080099999999999</v>
+        <v>0.061982000000000002</v>
       </c>
       <c r="D58" s="475">
-        <v>-4.0899999999999999</v>
+        <v>-4.1100000000000003</v>
       </c>
       <c r="E58" s="476">
         <v>0</v>
       </c>
       <c r="F58" s="477">
-        <v>0.58145480000000005</v>
+        <v>0.580596</v>
       </c>
       <c r="G58" s="478">
-        <v>0.82605620000000002</v>
+        <v>0.82481090000000001</v>
       </c>
     </row>
     <row r="59">
@@ -11541,22 +11541,22 @@
         <v>54</v>
       </c>
       <c r="B59" s="481">
-        <v>1.2488999999999999</v>
+        <v>1.2476400000000001</v>
       </c>
       <c r="C59" s="482">
-        <v>0.1096491</v>
+        <v>0.1095322</v>
       </c>
       <c r="D59" s="483">
-        <v>2.5299999999999998</v>
+        <v>2.52</v>
       </c>
       <c r="E59" s="484">
-        <v>0.010999999999999999</v>
+        <v>0.012</v>
       </c>
       <c r="F59" s="485">
-        <v>1.051466</v>
+        <v>1.0504150000000001</v>
       </c>
       <c r="G59" s="486">
-        <v>1.4834069999999999</v>
+        <v>1.481895</v>
       </c>
     </row>
     <row r="60">
@@ -11564,22 +11564,22 @@
         <v>55</v>
       </c>
       <c r="B60" s="489">
-        <v>0.45302170000000003</v>
+        <v>0.4519531</v>
       </c>
       <c r="C60" s="490">
-        <v>0.4570883</v>
+        <v>0.4559897</v>
       </c>
       <c r="D60" s="491">
-        <v>-0.78000000000000003</v>
+        <v>-0.79000000000000004</v>
       </c>
       <c r="E60" s="492">
-        <v>0.433</v>
+        <v>0.431</v>
       </c>
       <c r="F60" s="493">
-        <v>0.062701300000000001</v>
+        <v>0.062558900000000001</v>
       </c>
       <c r="G60" s="494">
-        <v>3.2731159999999999</v>
+        <v>3.2651059999999999</v>
       </c>
     </row>
     <row r="61">
@@ -11587,22 +11587,22 @@
         <v>56</v>
       </c>
       <c r="B61" s="497">
-        <v>0.86564149999999995</v>
+        <v>0.86644790000000005</v>
       </c>
       <c r="C61" s="498">
-        <v>0.033577099999999999</v>
+        <v>0.0336032</v>
       </c>
       <c r="D61" s="499">
-        <v>-3.7200000000000002</v>
+        <v>-3.7000000000000002</v>
       </c>
       <c r="E61" s="500">
         <v>0</v>
       </c>
       <c r="F61" s="501">
-        <v>0.80227090000000001</v>
+        <v>0.80302770000000001</v>
       </c>
       <c r="G61" s="502">
-        <v>0.93401769999999995</v>
+        <v>0.9348767</v>
       </c>
     </row>
     <row r="62">
@@ -11610,22 +11610,22 @@
         <v>57</v>
       </c>
       <c r="B62" s="505">
-        <v>1.129859</v>
+        <v>1.128463</v>
       </c>
       <c r="C62" s="506">
-        <v>0.051470200000000001</v>
+        <v>0.051392500000000001</v>
       </c>
       <c r="D62" s="507">
-        <v>2.6800000000000002</v>
+        <v>2.6499999999999999</v>
       </c>
       <c r="E62" s="508">
-        <v>0.0070000000000000001</v>
+        <v>0.0080000000000000002</v>
       </c>
       <c r="F62" s="509">
-        <v>1.033352</v>
+        <v>1.0321</v>
       </c>
       <c r="G62" s="510">
-        <v>1.2353799999999999</v>
+        <v>1.2338229999999999</v>
       </c>
     </row>
     <row r="63">
@@ -11633,22 +11633,22 @@
         <v>58</v>
       </c>
       <c r="B63" s="513">
-        <v>0.93315870000000001</v>
+        <v>0.93404089999999995</v>
       </c>
       <c r="C63" s="514">
-        <v>0.033945299999999998</v>
+        <v>0.033977</v>
       </c>
       <c r="D63" s="515">
-        <v>-1.8999999999999999</v>
+        <v>-1.8799999999999999</v>
       </c>
       <c r="E63" s="516">
-        <v>0.057000000000000002</v>
+        <v>0.060999999999999999</v>
       </c>
       <c r="F63" s="517">
-        <v>0.86894349999999998</v>
+        <v>0.86976569999999998</v>
       </c>
       <c r="G63" s="518">
-        <v>1.0021199999999999</v>
+        <v>1.003066</v>
       </c>
     </row>
     <row r="64">
@@ -11656,22 +11656,22 @@
         <v>59</v>
       </c>
       <c r="B64" s="521">
-        <v>1.2892509999999999</v>
+        <v>1.2885549999999999</v>
       </c>
       <c r="C64" s="522">
-        <v>0.117183</v>
+        <v>0.11709700000000001</v>
       </c>
       <c r="D64" s="523">
-        <v>2.7999999999999998</v>
+        <v>2.79</v>
       </c>
       <c r="E64" s="524">
         <v>0.0050000000000000001</v>
       </c>
       <c r="F64" s="525">
-        <v>1.0788720000000001</v>
+        <v>1.0783259999999999</v>
       </c>
       <c r="G64" s="526">
-        <v>1.540654</v>
+        <v>1.539769</v>
       </c>
     </row>
     <row r="65">
@@ -11679,22 +11679,22 @@
         <v>60</v>
       </c>
       <c r="B65" s="529">
-        <v>1.5350360000000001</v>
+        <v>1.5311650000000001</v>
       </c>
       <c r="C65" s="530">
-        <v>0.2199845</v>
+        <v>0.219363</v>
       </c>
       <c r="D65" s="531">
-        <v>2.9900000000000002</v>
+        <v>2.9700000000000002</v>
       </c>
       <c r="E65" s="532">
         <v>0.0030000000000000001</v>
       </c>
       <c r="F65" s="533">
-        <v>1.1591340000000001</v>
+        <v>1.15631</v>
       </c>
       <c r="G65" s="534">
-        <v>2.0328409999999999</v>
+        <v>2.0275409999999998</v>
       </c>
     </row>
     <row r="66">
@@ -11702,10 +11702,10 @@
         <v>61</v>
       </c>
       <c r="B66" s="537">
-        <v>0.24660550000000001</v>
+        <v>0.24709629999999999</v>
       </c>
       <c r="C66" s="538">
-        <v>0.32937070000000002</v>
+        <v>0.33007350000000002</v>
       </c>
       <c r="D66" s="539">
         <v>-1.05</v>
@@ -11714,10 +11714,10 @@
         <v>0.29499999999999999</v>
       </c>
       <c r="F66" s="541">
-        <v>0.017993800000000001</v>
+        <v>0.018022799999999999</v>
       </c>
       <c r="G66" s="542">
-        <v>3.379737</v>
+        <v>3.3877329999999999</v>
       </c>
     </row>
     <row r="67">
@@ -11725,22 +11725,22 @@
         <v>62</v>
       </c>
       <c r="B67" s="545">
-        <v>0.99161860000000002</v>
+        <v>0.99148409999999998</v>
       </c>
       <c r="C67" s="546">
-        <v>0.058427199999999999</v>
+        <v>0.058413</v>
       </c>
       <c r="D67" s="547">
-        <v>-0.14000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="E67" s="548">
-        <v>0.88600000000000001</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="F67" s="549">
-        <v>0.88346829999999999</v>
+        <v>0.88335940000000002</v>
       </c>
       <c r="G67" s="550">
-        <v>1.113008</v>
+        <v>1.112843</v>
       </c>
     </row>
     <row r="68">
@@ -11748,22 +11748,22 @@
         <v>63</v>
       </c>
       <c r="B68" s="553">
-        <v>1.2761499999999999</v>
+        <v>1.2773650000000001</v>
       </c>
       <c r="C68" s="554">
-        <v>0.085813799999999996</v>
+        <v>0.085905999999999996</v>
       </c>
       <c r="D68" s="555">
-        <v>3.6299999999999999</v>
+        <v>3.6400000000000001</v>
       </c>
       <c r="E68" s="556">
         <v>0</v>
       </c>
       <c r="F68" s="557">
-        <v>1.1185700000000001</v>
+        <v>1.119618</v>
       </c>
       <c r="G68" s="558">
-        <v>1.455929</v>
+        <v>1.457339</v>
       </c>
     </row>
     <row r="69">
@@ -11771,22 +11771,22 @@
         <v>64</v>
       </c>
       <c r="B69" s="561">
-        <v>1.2272650000000001</v>
+        <v>1.229684</v>
       </c>
       <c r="C69" s="562">
-        <v>0.1074454</v>
+        <v>0.10766149999999999</v>
       </c>
       <c r="D69" s="563">
-        <v>2.3399999999999999</v>
+        <v>2.3599999999999999</v>
       </c>
       <c r="E69" s="564">
-        <v>0.019</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="F69" s="565">
-        <v>1.0337529999999999</v>
+        <v>1.035784</v>
       </c>
       <c r="G69" s="566">
-        <v>1.457001</v>
+        <v>1.459884</v>
       </c>
     </row>
     <row r="70">
@@ -11794,22 +11794,22 @@
         <v>65</v>
       </c>
       <c r="B70" s="569">
-        <v>0.63270329999999997</v>
+        <v>0.62965070000000001</v>
       </c>
       <c r="C70" s="570">
-        <v>0.27850580000000003</v>
+        <v>0.27697549999999999</v>
       </c>
       <c r="D70" s="571">
-        <v>-1.04</v>
+        <v>-1.05</v>
       </c>
       <c r="E70" s="572">
-        <v>0.29799999999999999</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="F70" s="573">
-        <v>0.26700220000000002</v>
+        <v>0.2658684</v>
       </c>
       <c r="G70" s="574">
-        <v>1.4992890000000001</v>
+        <v>1.4911890000000001</v>
       </c>
     </row>
     <row r="71">
@@ -11817,22 +11817,22 @@
         <v>66</v>
       </c>
       <c r="B71" s="577">
-        <v>1.9363870000000001</v>
+        <v>1.94034</v>
       </c>
       <c r="C71" s="578">
-        <v>0.3035931</v>
+        <v>0.30414930000000001</v>
       </c>
       <c r="D71" s="579">
-        <v>4.21</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="E71" s="580">
         <v>0</v>
       </c>
       <c r="F71" s="581">
-        <v>1.424091</v>
+        <v>1.42709</v>
       </c>
       <c r="G71" s="582">
-        <v>2.6329720000000001</v>
+        <v>2.6381779999999999</v>
       </c>
     </row>
     <row r="72">
@@ -11840,22 +11840,22 @@
         <v>67</v>
       </c>
       <c r="B72" s="585">
-        <v>1.0026330000000001</v>
+        <v>1.001576</v>
       </c>
       <c r="C72" s="586">
-        <v>0.17313439999999999</v>
+        <v>0.17293890000000001</v>
       </c>
       <c r="D72" s="587">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E72" s="588">
-        <v>0.98799999999999999</v>
+        <v>0.99299999999999999</v>
       </c>
       <c r="F72" s="589">
-        <v>0.71475420000000001</v>
+        <v>0.71401879999999995</v>
       </c>
       <c r="G72" s="590">
-        <v>1.40646</v>
+        <v>1.404941</v>
       </c>
     </row>
     <row r="73">
@@ -11863,22 +11863,22 @@
         <v>68</v>
       </c>
       <c r="B73" s="593">
-        <v>0.95309200000000005</v>
+        <v>0.95334750000000001</v>
       </c>
       <c r="C73" s="594">
-        <v>0.076392500000000002</v>
+        <v>0.0764156</v>
       </c>
       <c r="D73" s="595">
         <v>-0.59999999999999998</v>
       </c>
       <c r="E73" s="596">
-        <v>0.54900000000000004</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="F73" s="597">
-        <v>0.81453379999999998</v>
+        <v>0.81474780000000002</v>
       </c>
       <c r="G73" s="598">
-        <v>1.1152200000000001</v>
+        <v>1.1155250000000001</v>
       </c>
     </row>
     <row r="74">
@@ -11886,22 +11886,22 @@
         <v>69</v>
       </c>
       <c r="B74" s="601">
-        <v>1.136344</v>
+        <v>1.1366540000000001</v>
       </c>
       <c r="C74" s="602">
-        <v>0.12661159999999999</v>
+        <v>0.1266128</v>
       </c>
       <c r="D74" s="603">
         <v>1.1499999999999999</v>
       </c>
       <c r="E74" s="604">
-        <v>0.251</v>
+        <v>0.25</v>
       </c>
       <c r="F74" s="605">
-        <v>0.91341649999999997</v>
+        <v>0.91371860000000005</v>
       </c>
       <c r="G74" s="606">
-        <v>1.4136789999999999</v>
+        <v>1.4139839999999999</v>
       </c>
     </row>
     <row r="75">
@@ -11909,22 +11909,22 @@
         <v>70</v>
       </c>
       <c r="B75" s="609">
-        <v>1.017245</v>
+        <v>1.0105789999999999</v>
       </c>
       <c r="C75" s="610">
-        <v>0.036282300000000004</v>
+        <v>0.035886599999999998</v>
       </c>
       <c r="D75" s="611">
-        <v>0.47999999999999998</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="E75" s="612">
-        <v>0.63200000000000001</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="F75" s="613">
-        <v>0.94856189999999996</v>
+        <v>0.94263450000000004</v>
       </c>
       <c r="G75" s="614">
-        <v>1.090902</v>
+        <v>1.083421</v>
       </c>
     </row>
     <row r="76">
@@ -11932,22 +11932,22 @@
         <v>71</v>
       </c>
       <c r="B76" s="617">
-        <v>1.3648549999999999</v>
+        <v>1.341038</v>
       </c>
       <c r="C76" s="618">
-        <v>0.11955250000000001</v>
+        <v>0.1168526</v>
       </c>
       <c r="D76" s="619">
-        <v>3.5499999999999998</v>
+        <v>3.3700000000000001</v>
       </c>
       <c r="E76" s="620">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F76" s="621">
-        <v>1.1495470000000001</v>
+        <v>1.1305000000000001</v>
       </c>
       <c r="G76" s="622">
-        <v>1.62049</v>
+        <v>1.590784</v>
       </c>
     </row>
     <row r="77">
@@ -11955,22 +11955,22 @@
         <v>72</v>
       </c>
       <c r="B77" s="625">
-        <v>1.0294509999999999</v>
+        <v>1.0341370000000001</v>
       </c>
       <c r="C77" s="626">
-        <v>0.043019700000000001</v>
+        <v>0.043159500000000004</v>
       </c>
       <c r="D77" s="627">
-        <v>0.68999999999999995</v>
+        <v>0.80000000000000004</v>
       </c>
       <c r="E77" s="628">
-        <v>0.48699999999999999</v>
+        <v>0.42099999999999999</v>
       </c>
       <c r="F77" s="629">
-        <v>0.94849459999999997</v>
+        <v>0.95291269999999995</v>
       </c>
       <c r="G77" s="630">
-        <v>1.1173169999999999</v>
+        <v>1.1222840000000001</v>
       </c>
     </row>
     <row r="78">
@@ -11978,22 +11978,22 @@
         <v>73</v>
       </c>
       <c r="B78" s="633">
-        <v>1.114568</v>
+        <v>1.1118440000000001</v>
       </c>
       <c r="C78" s="634">
-        <v>0.1667701</v>
+        <v>0.1663501</v>
       </c>
       <c r="D78" s="635">
-        <v>0.71999999999999997</v>
+        <v>0.70999999999999997</v>
       </c>
       <c r="E78" s="636">
-        <v>0.46899999999999997</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="F78" s="637">
-        <v>0.83127189999999995</v>
+        <v>0.82925939999999998</v>
       </c>
       <c r="G78" s="638">
-        <v>1.49441</v>
+        <v>1.490726</v>
       </c>
     </row>
     <row r="79">
@@ -12001,22 +12001,22 @@
         <v>74</v>
       </c>
       <c r="B79" s="641">
-        <v>1.120684</v>
+        <v>1.1200490000000001</v>
       </c>
       <c r="C79" s="642">
-        <v>0.038473800000000002</v>
+        <v>0.038449400000000002</v>
       </c>
       <c r="D79" s="643">
-        <v>3.3199999999999999</v>
+        <v>3.2999999999999998</v>
       </c>
       <c r="E79" s="644">
         <v>0.001</v>
       </c>
       <c r="F79" s="645">
-        <v>1.047758</v>
+        <v>1.0471680000000001</v>
       </c>
       <c r="G79" s="646">
-        <v>1.1986859999999999</v>
+        <v>1.1980010000000001</v>
       </c>
     </row>
     <row r="80">
@@ -12024,22 +12024,22 @@
         <v>75</v>
       </c>
       <c r="B80" s="656">
-        <v>79.053520000000006</v>
+        <v>105.6007</v>
       </c>
       <c r="C80" s="657">
-        <v>35.161259999999999</v>
+        <v>44.021410000000003</v>
       </c>
       <c r="D80" s="658">
-        <v>9.8300000000000001</v>
+        <v>11.18</v>
       </c>
       <c r="E80" s="659">
         <v>0</v>
       </c>
       <c r="F80" s="660">
-        <v>33.061729999999997</v>
+        <v>46.647559999999999</v>
       </c>
       <c r="G80" s="661">
-        <v>189.024</v>
+        <v>239.05860000000001</v>
       </c>
     </row>
   </sheetData>

--- a/progression_odds_all.xlsx
+++ b/progression_odds_all.xlsx
@@ -10230,22 +10230,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="25">
-        <v>1.1886890000000001</v>
+        <v>1.357753</v>
       </c>
       <c r="C2" s="26">
-        <v>0.72803110000000004</v>
+        <v>0.22224630000000001</v>
       </c>
       <c r="D2" s="27">
-        <v>0.28000000000000003</v>
+        <v>1.8700000000000001</v>
       </c>
       <c r="E2" s="28">
-        <v>0.77800000000000002</v>
+        <v>0.062</v>
       </c>
       <c r="F2" s="29">
-        <v>0.35787950000000002</v>
+        <v>0.9851221</v>
       </c>
       <c r="G2" s="30">
-        <v>3.948207</v>
+        <v>1.8713329999999999</v>
       </c>
     </row>
     <row r="3">
@@ -10253,22 +10253,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="33">
-        <v>0.94679979999999997</v>
+        <v>1.253906</v>
       </c>
       <c r="C3" s="34">
-        <v>0.048501900000000001</v>
+        <v>0.1998722</v>
       </c>
       <c r="D3" s="35">
-        <v>-1.0700000000000001</v>
+        <v>1.4199999999999999</v>
       </c>
       <c r="E3" s="36">
-        <v>0.28599999999999998</v>
+        <v>0.156</v>
       </c>
       <c r="F3" s="37">
-        <v>0.85635430000000001</v>
+        <v>0.91745290000000002</v>
       </c>
       <c r="G3" s="38">
-        <v>1.0467979999999999</v>
+        <v>1.7137450000000001</v>
       </c>
     </row>
     <row r="4">
@@ -10276,22 +10276,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="41">
-        <v>1.605864</v>
+        <v>2.1276600000000001</v>
       </c>
       <c r="C4" s="42">
-        <v>0.13743710000000001</v>
+        <v>0.36961090000000002</v>
       </c>
       <c r="D4" s="43">
-        <v>5.5300000000000002</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="E4" s="44">
         <v>0</v>
       </c>
       <c r="F4" s="45">
-        <v>1.3578730000000001</v>
+        <v>1.5136799999999999</v>
       </c>
       <c r="G4" s="46">
-        <v>1.899146</v>
+        <v>2.9906839999999999</v>
       </c>
     </row>
     <row r="5">
@@ -10299,22 +10299,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="49">
-        <v>0.90028490000000005</v>
+        <v>1.1742509999999999</v>
       </c>
       <c r="C5" s="50">
-        <v>0.060673600000000001</v>
+        <v>0.18542449999999999</v>
       </c>
       <c r="D5" s="51">
-        <v>-1.5600000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="E5" s="52">
-        <v>0.11899999999999999</v>
+        <v>0.309</v>
       </c>
       <c r="F5" s="53">
-        <v>0.78888610000000003</v>
+        <v>0.8616857</v>
       </c>
       <c r="G5" s="54">
-        <v>1.027414</v>
+        <v>1.600196</v>
       </c>
     </row>
     <row r="6">
@@ -10322,22 +10322,22 @@
         <v>11</v>
       </c>
       <c r="B6" s="57">
-        <v>0.70913009999999999</v>
+        <v>1.1191800000000001</v>
       </c>
       <c r="C6" s="58">
-        <v>0.43342360000000002</v>
+        <v>0.18230270000000001</v>
       </c>
       <c r="D6" s="59">
-        <v>-0.56000000000000005</v>
+        <v>0.68999999999999995</v>
       </c>
       <c r="E6" s="60">
-        <v>0.57399999999999995</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="F6" s="61">
-        <v>0.21402650000000001</v>
+        <v>0.8132952</v>
       </c>
       <c r="G6" s="62">
-        <v>2.349548</v>
+        <v>1.5401100000000001</v>
       </c>
     </row>
     <row r="7">
@@ -10345,22 +10345,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="65">
-        <v>0.93782460000000001</v>
+        <v>1.2338610000000001</v>
       </c>
       <c r="C7" s="66">
-        <v>0.25536029999999999</v>
+        <v>0.38278040000000002</v>
       </c>
       <c r="D7" s="67">
-        <v>-0.23999999999999999</v>
+        <v>0.68000000000000005</v>
       </c>
       <c r="E7" s="68">
-        <v>0.81399999999999995</v>
+        <v>0.498</v>
       </c>
       <c r="F7" s="69">
-        <v>0.54998130000000001</v>
+        <v>0.67173519999999998</v>
       </c>
       <c r="G7" s="70">
-        <v>1.599173</v>
+        <v>2.2663880000000001</v>
       </c>
     </row>
     <row r="8">
@@ -10368,22 +10368,22 @@
         <v>13</v>
       </c>
       <c r="B8" s="73">
-        <v>0.82479139999999995</v>
+        <v>1.0313209999999999</v>
       </c>
       <c r="C8" s="74">
-        <v>0.60531800000000002</v>
+        <v>0.77493939999999995</v>
       </c>
       <c r="D8" s="75">
-        <v>-0.26000000000000001</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="E8" s="76">
-        <v>0.79300000000000004</v>
+        <v>0.96699999999999997</v>
       </c>
       <c r="F8" s="77">
-        <v>0.1957238</v>
+        <v>0.23648150000000001</v>
       </c>
       <c r="G8" s="78">
-        <v>3.4757189999999998</v>
+        <v>4.4977020000000003</v>
       </c>
     </row>
     <row r="9">
@@ -10391,22 +10391,22 @@
         <v>14</v>
       </c>
       <c r="B9" s="81">
-        <v>1.6323700000000001</v>
+        <v>2.1911230000000002</v>
       </c>
       <c r="C9" s="82">
-        <v>1.133365</v>
+        <v>1.560478</v>
       </c>
       <c r="D9" s="83">
-        <v>0.70999999999999997</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="E9" s="84">
-        <v>0.47999999999999998</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="F9" s="85">
-        <v>0.41862349999999998</v>
+        <v>0.54257040000000001</v>
       </c>
       <c r="G9" s="86">
-        <v>6.365221</v>
+        <v>8.8486550000000008</v>
       </c>
     </row>
     <row r="10">
@@ -10414,22 +10414,22 @@
         <v>15</v>
       </c>
       <c r="B10" s="89">
-        <v>0.76480170000000003</v>
+        <v>1.014059</v>
       </c>
       <c r="C10" s="90">
-        <v>0.153976</v>
+        <v>0.25553360000000003</v>
       </c>
       <c r="D10" s="91">
-        <v>-1.3300000000000001</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="E10" s="92">
-        <v>0.183</v>
+        <v>0.95599999999999996</v>
       </c>
       <c r="F10" s="93">
-        <v>0.51544000000000001</v>
+        <v>0.61882579999999998</v>
       </c>
       <c r="G10" s="94">
-        <v>1.134801</v>
+        <v>1.6617219999999999</v>
       </c>
     </row>
     <row r="11">
@@ -10437,22 +10437,22 @@
         <v>16</v>
       </c>
       <c r="B11" s="97">
-        <v>0.48209380000000002</v>
+        <v>0.63879359999999996</v>
       </c>
       <c r="C11" s="98">
-        <v>0.20411380000000001</v>
+        <v>0.28717300000000001</v>
       </c>
       <c r="D11" s="99">
-        <v>-1.72</v>
+        <v>-1</v>
       </c>
       <c r="E11" s="100">
-        <v>0.085000000000000006</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="F11" s="101">
-        <v>0.21025240000000001</v>
+        <v>0.26466620000000002</v>
       </c>
       <c r="G11" s="102">
-        <v>1.105407</v>
+        <v>1.5417810000000001</v>
       </c>
     </row>
     <row r="12">
@@ -10506,10 +10506,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="121">
-        <v>0.5561564</v>
+        <v>0.55623789999999995</v>
       </c>
       <c r="C14" s="122">
-        <v>0.063395099999999996</v>
+        <v>0.063396599999999997</v>
       </c>
       <c r="D14" s="123">
         <v>-5.1500000000000004</v>
@@ -10518,10 +10518,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="125">
-        <v>0.44480570000000003</v>
+        <v>0.44488299999999997</v>
       </c>
       <c r="G14" s="126">
-        <v>0.69538219999999995</v>
+        <v>0.69546509999999995</v>
       </c>
     </row>
     <row r="15">
@@ -10529,22 +10529,22 @@
         <v>19</v>
       </c>
       <c r="B15" s="129">
-        <v>1.049205</v>
+        <v>1.3255269999999999</v>
       </c>
       <c r="C15" s="130">
-        <v>0.68123420000000001</v>
+        <v>0.87381690000000001</v>
       </c>
       <c r="D15" s="131">
-        <v>0.070000000000000007</v>
+        <v>0.42999999999999999</v>
       </c>
       <c r="E15" s="132">
-        <v>0.94099999999999995</v>
+        <v>0.66900000000000004</v>
       </c>
       <c r="F15" s="133">
-        <v>0.29389159999999998</v>
+        <v>0.36413129999999999</v>
       </c>
       <c r="G15" s="134">
-        <v>3.7457060000000002</v>
+        <v>4.8252470000000001</v>
       </c>
     </row>
     <row r="16">
@@ -10552,22 +10552,22 @@
         <v>20</v>
       </c>
       <c r="B16" s="137">
-        <v>0.28876669999999999</v>
+        <v>0.37987500000000002</v>
       </c>
       <c r="C16" s="138">
-        <v>0.043010399999999997</v>
+        <v>0.079771599999999998</v>
       </c>
       <c r="D16" s="139">
-        <v>-8.3399999999999999</v>
+        <v>-4.6100000000000003</v>
       </c>
       <c r="E16" s="140">
         <v>0</v>
       </c>
       <c r="F16" s="141">
-        <v>0.2156576</v>
+        <v>0.25170569999999998</v>
       </c>
       <c r="G16" s="142">
-        <v>0.38666010000000001</v>
+        <v>0.57330840000000005</v>
       </c>
     </row>
     <row r="17">
@@ -10621,22 +10621,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="161">
-        <v>0.81664490000000001</v>
+        <v>0.81782580000000005</v>
       </c>
       <c r="C19" s="162">
-        <v>0.052333999999999999</v>
+        <v>0.052415499999999997</v>
       </c>
       <c r="D19" s="163">
-        <v>-3.1600000000000001</v>
+        <v>-3.1400000000000001</v>
       </c>
       <c r="E19" s="164">
         <v>0.002</v>
       </c>
       <c r="F19" s="165">
-        <v>0.72025249999999996</v>
+        <v>0.72128389999999998</v>
       </c>
       <c r="G19" s="166">
-        <v>0.92593769999999998</v>
+        <v>0.92728960000000005</v>
       </c>
     </row>
     <row r="20">
@@ -10644,22 +10644,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="169">
-        <v>1.27603</v>
+        <v>1.6772069999999999</v>
       </c>
       <c r="C20" s="170">
-        <v>0.135403</v>
+        <v>0.30474289999999998</v>
       </c>
       <c r="D20" s="171">
-        <v>2.2999999999999998</v>
+        <v>2.8500000000000001</v>
       </c>
       <c r="E20" s="172">
-        <v>0.021999999999999999</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="F20" s="173">
-        <v>1.036424</v>
+        <v>1.174698</v>
       </c>
       <c r="G20" s="174">
-        <v>1.571029</v>
+        <v>2.3946779999999999</v>
       </c>
     </row>
     <row r="21">
@@ -10667,22 +10667,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="177">
-        <v>0.46695419999999999</v>
+        <v>0.61454399999999998</v>
       </c>
       <c r="C21" s="178">
-        <v>0.027012000000000001</v>
+        <v>0.097524899999999998</v>
       </c>
       <c r="D21" s="179">
-        <v>-13.16</v>
+        <v>-3.0699999999999999</v>
       </c>
       <c r="E21" s="180">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F21" s="181">
-        <v>0.41690260000000001</v>
+        <v>0.45026860000000002</v>
       </c>
       <c r="G21" s="182">
-        <v>0.5230148</v>
+        <v>0.83875330000000003</v>
       </c>
     </row>
     <row r="22">
@@ -10736,22 +10736,22 @@
         <v>18</v>
       </c>
       <c r="B24" s="201">
-        <v>0.96339940000000002</v>
+        <v>0.96795949999999997</v>
       </c>
       <c r="C24" s="202">
-        <v>0.210422</v>
+        <v>0.21150189999999999</v>
       </c>
       <c r="D24" s="203">
-        <v>-0.17000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="E24" s="204">
-        <v>0.86399999999999999</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="F24" s="205">
-        <v>0.6278996</v>
+        <v>0.63076449999999995</v>
       </c>
       <c r="G24" s="206">
-        <v>1.478164</v>
+        <v>1.4854130000000001</v>
       </c>
     </row>
     <row r="25">
@@ -10759,22 +10759,22 @@
         <v>19</v>
       </c>
       <c r="B25" s="209">
-        <v>1.171556</v>
+        <v>1.535342</v>
       </c>
       <c r="C25" s="210">
-        <v>0.17995449999999999</v>
+        <v>0.3247602</v>
       </c>
       <c r="D25" s="211">
-        <v>1.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="E25" s="212">
-        <v>0.30299999999999999</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="F25" s="213">
-        <v>0.86699400000000004</v>
+        <v>1.014276</v>
       </c>
       <c r="G25" s="214">
-        <v>1.583107</v>
+        <v>2.3240949999999998</v>
       </c>
     </row>
     <row r="26">
@@ -10782,22 +10782,22 @@
         <v>20</v>
       </c>
       <c r="B26" s="217">
-        <v>0.79288069999999999</v>
+        <v>1.0342929999999999</v>
       </c>
       <c r="C26" s="218">
-        <v>0.17991550000000001</v>
+        <v>0.27796559999999998</v>
       </c>
       <c r="D26" s="219">
-        <v>-1.02</v>
+        <v>0.13</v>
       </c>
       <c r="E26" s="220">
-        <v>0.306</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="F26" s="221">
-        <v>0.50822789999999995</v>
+        <v>0.6107783</v>
       </c>
       <c r="G26" s="222">
-        <v>1.236964</v>
+        <v>1.7514730000000001</v>
       </c>
     </row>
     <row r="27">
@@ -10828,22 +10828,22 @@
         <v>23</v>
       </c>
       <c r="B28" s="233">
-        <v>0.97821290000000005</v>
+        <v>0.9788943</v>
       </c>
       <c r="C28" s="234">
-        <v>0.078256099999999995</v>
+        <v>0.078322900000000001</v>
       </c>
       <c r="D28" s="235">
-        <v>-0.28000000000000003</v>
+        <v>-0.27000000000000002</v>
       </c>
       <c r="E28" s="236">
-        <v>0.78300000000000003</v>
+        <v>0.79000000000000004</v>
       </c>
       <c r="F28" s="237">
-        <v>0.83625369999999999</v>
+        <v>0.83681559999999999</v>
       </c>
       <c r="G28" s="238">
-        <v>1.1442699999999999</v>
+        <v>1.1450959999999999</v>
       </c>
     </row>
     <row r="29">
@@ -10851,22 +10851,22 @@
         <v>24</v>
       </c>
       <c r="B29" s="241">
-        <v>1.1559729999999999</v>
+        <v>1.1550199999999999</v>
       </c>
       <c r="C29" s="242">
-        <v>0.045477499999999997</v>
+        <v>0.045443999999999998</v>
       </c>
       <c r="D29" s="243">
-        <v>3.6800000000000002</v>
+        <v>3.6600000000000001</v>
       </c>
       <c r="E29" s="244">
         <v>0</v>
       </c>
       <c r="F29" s="245">
-        <v>1.0701879999999999</v>
+        <v>1.069299</v>
       </c>
       <c r="G29" s="246">
-        <v>1.2486330000000001</v>
+        <v>1.2476130000000001</v>
       </c>
     </row>
     <row r="30">
@@ -10874,22 +10874,22 @@
         <v>25</v>
       </c>
       <c r="B30" s="249">
-        <v>0.46004050000000002</v>
+        <v>0.46026309999999998</v>
       </c>
       <c r="C30" s="250">
-        <v>0.019332499999999999</v>
+        <v>0.019343699999999998</v>
       </c>
       <c r="D30" s="251">
-        <v>-18.48</v>
+        <v>-18.460000000000001</v>
       </c>
       <c r="E30" s="252">
         <v>0</v>
       </c>
       <c r="F30" s="253">
-        <v>0.42366789999999999</v>
+        <v>0.42386970000000002</v>
       </c>
       <c r="G30" s="254">
-        <v>0.49953570000000003</v>
+        <v>0.49978129999999998</v>
       </c>
     </row>
     <row r="31">
@@ -10897,22 +10897,22 @@
         <v>26</v>
       </c>
       <c r="B31" s="257">
-        <v>0.73609559999999996</v>
+        <v>0.73555570000000003</v>
       </c>
       <c r="C31" s="258">
-        <v>0.026760200000000001</v>
+        <v>0.0267435</v>
       </c>
       <c r="D31" s="259">
-        <v>-8.4299999999999997</v>
+        <v>-8.4499999999999993</v>
       </c>
       <c r="E31" s="260">
         <v>0</v>
       </c>
       <c r="F31" s="261">
-        <v>0.68547150000000001</v>
+        <v>0.6849634</v>
       </c>
       <c r="G31" s="262">
-        <v>0.79045829999999995</v>
+        <v>0.7898847</v>
       </c>
     </row>
     <row r="32">
@@ -10920,22 +10920,22 @@
         <v>27</v>
       </c>
       <c r="B32" s="265">
-        <v>1.0959410000000001</v>
+        <v>1.0949180000000001</v>
       </c>
       <c r="C32" s="266">
-        <v>0.043862100000000001</v>
+        <v>0.043825700000000002</v>
       </c>
       <c r="D32" s="267">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="E32" s="268">
-        <v>0.021999999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="F32" s="269">
-        <v>1.013258</v>
+        <v>1.0123040000000001</v>
       </c>
       <c r="G32" s="270">
-        <v>1.185371</v>
+        <v>1.184274</v>
       </c>
     </row>
     <row r="33">
@@ -10943,22 +10943,22 @@
         <v>28</v>
       </c>
       <c r="B33" s="273">
-        <v>1.453908</v>
+        <v>1.451665</v>
       </c>
       <c r="C33" s="274">
-        <v>0.069554099999999994</v>
+        <v>0.069461300000000004</v>
       </c>
       <c r="D33" s="275">
-        <v>7.8200000000000003</v>
+        <v>7.79</v>
       </c>
       <c r="E33" s="276">
         <v>0</v>
       </c>
       <c r="F33" s="277">
-        <v>1.32378</v>
+        <v>1.321712</v>
       </c>
       <c r="G33" s="278">
-        <v>1.596827</v>
+        <v>1.594395</v>
       </c>
     </row>
     <row r="34">
@@ -10966,22 +10966,22 @@
         <v>29</v>
       </c>
       <c r="B34" s="281">
-        <v>1.4377819999999999</v>
+        <v>1.432834</v>
       </c>
       <c r="C34" s="282">
-        <v>0.1531209</v>
+        <v>0.1526103</v>
       </c>
       <c r="D34" s="283">
-        <v>3.4100000000000001</v>
+        <v>3.3799999999999999</v>
       </c>
       <c r="E34" s="284">
         <v>0.001</v>
       </c>
       <c r="F34" s="285">
-        <v>1.166922</v>
+        <v>1.1628799999999999</v>
       </c>
       <c r="G34" s="286">
-        <v>1.771512</v>
+        <v>1.7654559999999999</v>
       </c>
     </row>
     <row r="35">
@@ -10989,22 +10989,22 @@
         <v>30</v>
       </c>
       <c r="B35" s="289">
-        <v>0.97263569999999999</v>
+        <v>0.97140219999999999</v>
       </c>
       <c r="C35" s="290">
-        <v>0.064271499999999995</v>
+        <v>0.064196500000000004</v>
       </c>
       <c r="D35" s="291">
-        <v>-0.41999999999999999</v>
+        <v>-0.44</v>
       </c>
       <c r="E35" s="292">
-        <v>0.67500000000000004</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="F35" s="293">
-        <v>0.85448230000000003</v>
+        <v>0.85338749999999997</v>
       </c>
       <c r="G35" s="294">
-        <v>1.107127</v>
+        <v>1.105737</v>
       </c>
     </row>
     <row r="36">
@@ -11012,10 +11012,10 @@
         <v>31</v>
       </c>
       <c r="B36" s="297">
-        <v>0.82177500000000003</v>
+        <v>0.82194829999999997</v>
       </c>
       <c r="C36" s="298">
-        <v>0.051496500000000001</v>
+        <v>0.0515112</v>
       </c>
       <c r="D36" s="299">
         <v>-3.1299999999999999</v>
@@ -11024,10 +11024,10 @@
         <v>0.002</v>
       </c>
       <c r="F36" s="301">
-        <v>0.72679579999999999</v>
+        <v>0.72694239999999999</v>
       </c>
       <c r="G36" s="302">
-        <v>0.9291663</v>
+        <v>0.92937060000000005</v>
       </c>
     </row>
     <row r="37">
@@ -11035,22 +11035,22 @@
         <v>32</v>
       </c>
       <c r="B37" s="305">
-        <v>0.54847780000000002</v>
+        <v>0.54424380000000006</v>
       </c>
       <c r="C37" s="306">
-        <v>0.0304373</v>
+        <v>0.030286</v>
       </c>
       <c r="D37" s="307">
-        <v>-10.82</v>
+        <v>-10.93</v>
       </c>
       <c r="E37" s="308">
         <v>0</v>
       </c>
       <c r="F37" s="309">
-        <v>0.49195159999999999</v>
+        <v>0.48800690000000002</v>
       </c>
       <c r="G37" s="310">
-        <v>0.61149900000000001</v>
+        <v>0.60696130000000004</v>
       </c>
     </row>
     <row r="38">
@@ -11058,22 +11058,22 @@
         <v>33</v>
       </c>
       <c r="B38" s="313">
-        <v>0.86998880000000001</v>
+        <v>0.86982150000000003</v>
       </c>
       <c r="C38" s="314">
-        <v>0.060043600000000003</v>
+        <v>0.060025799999999997</v>
       </c>
       <c r="D38" s="315">
         <v>-2.02</v>
       </c>
       <c r="E38" s="316">
-        <v>0.043999999999999998</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="F38" s="317">
-        <v>0.75991790000000004</v>
+        <v>0.75978259999999998</v>
       </c>
       <c r="G38" s="318">
-        <v>0.99600310000000003</v>
+        <v>0.99579740000000005</v>
       </c>
     </row>
     <row r="39">
@@ -11081,22 +11081,22 @@
         <v>34</v>
       </c>
       <c r="B39" s="321">
-        <v>1.0078290000000001</v>
+        <v>1.0085120000000001</v>
       </c>
       <c r="C39" s="322">
-        <v>0.0064399000000000001</v>
+        <v>0.0064542999999999996</v>
       </c>
       <c r="D39" s="323">
-        <v>1.22</v>
+        <v>1.3200000000000001</v>
       </c>
       <c r="E39" s="324">
-        <v>0.222</v>
+        <v>0.185</v>
       </c>
       <c r="F39" s="325">
-        <v>0.99528539999999999</v>
+        <v>0.99594070000000001</v>
       </c>
       <c r="G39" s="326">
-        <v>1.0205299999999999</v>
+        <v>1.021242</v>
       </c>
     </row>
     <row r="40">
@@ -11104,22 +11104,22 @@
         <v>35</v>
       </c>
       <c r="B40" s="329">
-        <v>0.46862959999999998</v>
+        <v>0.46828930000000002</v>
       </c>
       <c r="C40" s="330">
-        <v>0.043056900000000002</v>
+        <v>0.043027799999999998</v>
       </c>
       <c r="D40" s="331">
-        <v>-8.25</v>
+        <v>-8.2599999999999998</v>
       </c>
       <c r="E40" s="332">
         <v>0</v>
       </c>
       <c r="F40" s="333">
-        <v>0.39140180000000002</v>
+        <v>0.39111390000000001</v>
       </c>
       <c r="G40" s="334">
-        <v>0.56109529999999996</v>
+        <v>0.56069310000000006</v>
       </c>
     </row>
     <row r="41">
@@ -11127,10 +11127,10 @@
         <v>36</v>
       </c>
       <c r="B41" s="337">
-        <v>0.85479859999999997</v>
+        <v>0.85472570000000003</v>
       </c>
       <c r="C41" s="338">
-        <v>0.038996799999999998</v>
+        <v>0.0389959</v>
       </c>
       <c r="D41" s="339">
         <v>-3.44</v>
@@ -11139,10 +11139,10 @@
         <v>0.001</v>
       </c>
       <c r="F41" s="341">
-        <v>0.78168380000000004</v>
+        <v>0.78161270000000005</v>
       </c>
       <c r="G41" s="342">
-        <v>0.93475229999999998</v>
+        <v>0.93467769999999995</v>
       </c>
     </row>
     <row r="42">
@@ -11150,22 +11150,22 @@
         <v>37</v>
       </c>
       <c r="B42" s="345">
-        <v>0.86625640000000004</v>
+        <v>0.86567079999999996</v>
       </c>
       <c r="C42" s="346">
-        <v>0.072420899999999996</v>
+        <v>0.072383100000000006</v>
       </c>
       <c r="D42" s="347">
-        <v>-1.72</v>
+        <v>-1.73</v>
       </c>
       <c r="E42" s="348">
-        <v>0.085999999999999993</v>
+        <v>0.084000000000000005</v>
       </c>
       <c r="F42" s="349">
-        <v>0.73533320000000002</v>
+        <v>0.73481770000000002</v>
       </c>
       <c r="G42" s="350">
-        <v>1.0204899999999999</v>
+        <v>1.0198259999999999</v>
       </c>
     </row>
     <row r="43">
@@ -11173,22 +11173,22 @@
         <v>38</v>
       </c>
       <c r="B43" s="353">
-        <v>0.79460399999999998</v>
+        <v>0.79498020000000003</v>
       </c>
       <c r="C43" s="354">
-        <v>0.047350999999999997</v>
+        <v>0.047374800000000002</v>
       </c>
       <c r="D43" s="355">
-        <v>-3.8599999999999999</v>
+        <v>-3.8500000000000001</v>
       </c>
       <c r="E43" s="356">
         <v>0</v>
       </c>
       <c r="F43" s="357">
-        <v>0.70701250000000004</v>
+        <v>0.7073448</v>
       </c>
       <c r="G43" s="358">
-        <v>0.89304729999999999</v>
+        <v>0.89347299999999996</v>
       </c>
     </row>
     <row r="44">
@@ -11196,10 +11196,10 @@
         <v>39</v>
       </c>
       <c r="B44" s="361">
-        <v>0.86954600000000004</v>
+        <v>0.86984159999999999</v>
       </c>
       <c r="C44" s="362">
-        <v>0.050413399999999997</v>
+        <v>0.050432900000000003</v>
       </c>
       <c r="D44" s="363">
         <v>-2.4100000000000001</v>
@@ -11208,10 +11208,10 @@
         <v>0.016</v>
       </c>
       <c r="F44" s="365">
-        <v>0.77614470000000002</v>
+        <v>0.7764044</v>
       </c>
       <c r="G44" s="366">
-        <v>0.97418720000000003</v>
+        <v>0.97452349999999999</v>
       </c>
     </row>
     <row r="45">
@@ -11219,22 +11219,22 @@
         <v>40</v>
       </c>
       <c r="B45" s="369">
-        <v>0.7707387</v>
+        <v>0.77263300000000001</v>
       </c>
       <c r="C45" s="370">
-        <v>0.26000640000000003</v>
+        <v>0.26068390000000002</v>
       </c>
       <c r="D45" s="371">
-        <v>-0.77000000000000002</v>
+        <v>-0.76000000000000001</v>
       </c>
       <c r="E45" s="372">
-        <v>0.44</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F45" s="373">
-        <v>0.39788440000000003</v>
+        <v>0.3988234</v>
       </c>
       <c r="G45" s="374">
-        <v>1.4929920000000001</v>
+        <v>1.496807</v>
       </c>
     </row>
     <row r="46">
@@ -11242,22 +11242,22 @@
         <v>41</v>
       </c>
       <c r="B46" s="377">
-        <v>1.1536090000000001</v>
+        <v>1.153386</v>
       </c>
       <c r="C46" s="378">
-        <v>0.028707099999999999</v>
+        <v>0.028703099999999999</v>
       </c>
       <c r="D46" s="379">
-        <v>5.7400000000000002</v>
+        <v>5.7300000000000004</v>
       </c>
       <c r="E46" s="380">
         <v>0</v>
       </c>
       <c r="F46" s="381">
-        <v>1.0986940000000001</v>
+        <v>1.098479</v>
       </c>
       <c r="G46" s="382">
-        <v>1.211268</v>
+        <v>1.2110380000000001</v>
       </c>
     </row>
     <row r="47">
@@ -11265,22 +11265,22 @@
         <v>42</v>
       </c>
       <c r="B47" s="385">
-        <v>0.9690183</v>
+        <v>0.9694874</v>
       </c>
       <c r="C47" s="386">
-        <v>0.0146102</v>
+        <v>0.0146201</v>
       </c>
       <c r="D47" s="387">
-        <v>-2.0899999999999999</v>
+        <v>-2.0499999999999998</v>
       </c>
       <c r="E47" s="388">
-        <v>0.036999999999999998</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="F47" s="389">
-        <v>0.94080180000000002</v>
+        <v>0.94125190000000003</v>
       </c>
       <c r="G47" s="390">
-        <v>0.9980812</v>
+        <v>0.99856990000000001</v>
       </c>
     </row>
     <row r="48">
@@ -11288,22 +11288,22 @@
         <v>43</v>
       </c>
       <c r="B48" s="393">
-        <v>0.76178140000000005</v>
+        <v>0.76144999999999996</v>
       </c>
       <c r="C48" s="394">
-        <v>0.0279879</v>
+        <v>0.027975300000000002</v>
       </c>
       <c r="D48" s="395">
-        <v>-7.4100000000000001</v>
+        <v>-7.4199999999999999</v>
       </c>
       <c r="E48" s="396">
         <v>0</v>
       </c>
       <c r="F48" s="397">
-        <v>0.7088546</v>
+        <v>0.70854709999999999</v>
       </c>
       <c r="G48" s="398">
-        <v>0.81866000000000005</v>
+        <v>0.81830290000000006</v>
       </c>
     </row>
     <row r="49">
@@ -11311,22 +11311,22 @@
         <v>44</v>
       </c>
       <c r="B49" s="401">
-        <v>0.9098733</v>
+        <v>0.91014459999999997</v>
       </c>
       <c r="C49" s="402">
-        <v>0.047814099999999998</v>
+        <v>0.047829200000000002</v>
       </c>
       <c r="D49" s="403">
-        <v>-1.8</v>
+        <v>-1.79</v>
       </c>
       <c r="E49" s="404">
-        <v>0.071999999999999995</v>
+        <v>0.072999999999999996</v>
       </c>
       <c r="F49" s="405">
-        <v>0.82082390000000005</v>
+        <v>0.8210672</v>
       </c>
       <c r="G49" s="406">
-        <v>1.008583</v>
+        <v>1.008886</v>
       </c>
     </row>
     <row r="50">
@@ -11334,22 +11334,22 @@
         <v>45</v>
       </c>
       <c r="B50" s="409">
-        <v>0.84295730000000002</v>
+        <v>0.84242360000000005</v>
       </c>
       <c r="C50" s="410">
-        <v>0.022556400000000001</v>
+        <v>0.022545200000000001</v>
       </c>
       <c r="D50" s="411">
-        <v>-6.3799999999999999</v>
+        <v>-6.4100000000000001</v>
       </c>
       <c r="E50" s="412">
         <v>0</v>
       </c>
       <c r="F50" s="413">
-        <v>0.79988680000000001</v>
+        <v>0.79937480000000005</v>
       </c>
       <c r="G50" s="414">
-        <v>0.888347</v>
+        <v>0.88779079999999999</v>
       </c>
     </row>
     <row r="51">
@@ -11357,10 +11357,10 @@
         <v>46</v>
       </c>
       <c r="B51" s="417">
-        <v>0.7867497</v>
+        <v>0.78679299999999997</v>
       </c>
       <c r="C51" s="418">
-        <v>0.051803500000000002</v>
+        <v>0.051798299999999999</v>
       </c>
       <c r="D51" s="419">
         <v>-3.6400000000000001</v>
@@ -11369,10 +11369,10 @@
         <v>0</v>
       </c>
       <c r="F51" s="421">
-        <v>0.69149539999999998</v>
+        <v>0.69154720000000003</v>
       </c>
       <c r="G51" s="422">
-        <v>0.89512539999999996</v>
+        <v>0.89515690000000003</v>
       </c>
     </row>
     <row r="52">
@@ -11380,22 +11380,22 @@
         <v>47</v>
       </c>
       <c r="B52" s="425">
-        <v>0.91430699999999998</v>
+        <v>0.9147092</v>
       </c>
       <c r="C52" s="426">
-        <v>0.0472536</v>
+        <v>0.0472746</v>
       </c>
       <c r="D52" s="427">
-        <v>-1.73</v>
+        <v>-1.72</v>
       </c>
       <c r="E52" s="428">
-        <v>0.083000000000000004</v>
+        <v>0.085000000000000006</v>
       </c>
       <c r="F52" s="429">
-        <v>0.82622790000000002</v>
+        <v>0.82659110000000002</v>
       </c>
       <c r="G52" s="430">
-        <v>1.011776</v>
+        <v>1.012221</v>
       </c>
     </row>
     <row r="53">
@@ -11403,22 +11403,22 @@
         <v>48</v>
       </c>
       <c r="B53" s="433">
-        <v>0.92320159999999996</v>
+        <v>0.92288820000000005</v>
       </c>
       <c r="C53" s="434">
-        <v>0.0235</v>
+        <v>0.023492900000000001</v>
       </c>
       <c r="D53" s="435">
-        <v>-3.1400000000000001</v>
+        <v>-3.1499999999999999</v>
       </c>
       <c r="E53" s="436">
         <v>0.002</v>
       </c>
       <c r="F53" s="437">
-        <v>0.87827250000000001</v>
+        <v>0.8779728</v>
       </c>
       <c r="G53" s="438">
-        <v>0.97042910000000004</v>
+        <v>0.97010130000000006</v>
       </c>
     </row>
     <row r="54">
@@ -11426,22 +11426,22 @@
         <v>49</v>
       </c>
       <c r="B54" s="441">
-        <v>0.81269049999999998</v>
+        <v>0.81285079999999999</v>
       </c>
       <c r="C54" s="442">
-        <v>0.021414800000000001</v>
+        <v>0.021420000000000002</v>
       </c>
       <c r="D54" s="443">
-        <v>-7.8700000000000001</v>
+        <v>-7.8600000000000003</v>
       </c>
       <c r="E54" s="444">
         <v>0</v>
       </c>
       <c r="F54" s="445">
-        <v>0.77178369999999996</v>
+        <v>0.77193409999999996</v>
       </c>
       <c r="G54" s="446">
-        <v>0.85576549999999996</v>
+        <v>0.85593629999999998</v>
       </c>
     </row>
     <row r="55">
@@ -11449,22 +11449,22 @@
         <v>50</v>
       </c>
       <c r="B55" s="449">
-        <v>0.77146369999999998</v>
+        <v>0.77340529999999996</v>
       </c>
       <c r="C55" s="450">
-        <v>1.0973809999999999</v>
+        <v>1.1001270000000001</v>
       </c>
       <c r="D55" s="451">
         <v>-0.17999999999999999</v>
       </c>
       <c r="E55" s="452">
-        <v>0.85499999999999998</v>
+        <v>0.85699999999999999</v>
       </c>
       <c r="F55" s="453">
-        <v>0.047480000000000001</v>
+        <v>0.047601400000000002</v>
       </c>
       <c r="G55" s="454">
-        <v>12.534890000000001</v>
+        <v>12.56593</v>
       </c>
     </row>
     <row r="56">
@@ -11472,22 +11472,22 @@
         <v>51</v>
       </c>
       <c r="B56" s="457">
-        <v>0.72507219999999995</v>
+        <v>0.72609999999999997</v>
       </c>
       <c r="C56" s="458">
-        <v>0.068854299999999993</v>
+        <v>0.068958000000000005</v>
       </c>
       <c r="D56" s="459">
-        <v>-3.3900000000000001</v>
+        <v>-3.3700000000000001</v>
       </c>
       <c r="E56" s="460">
         <v>0.001</v>
       </c>
       <c r="F56" s="461">
-        <v>0.60193470000000004</v>
+        <v>0.60277809999999998</v>
       </c>
       <c r="G56" s="462">
-        <v>0.87339979999999995</v>
+        <v>0.87465210000000004</v>
       </c>
     </row>
     <row r="57">
@@ -11495,22 +11495,22 @@
         <v>52</v>
       </c>
       <c r="B57" s="465">
-        <v>0.88655709999999999</v>
+        <v>0.88618260000000004</v>
       </c>
       <c r="C57" s="466">
-        <v>0.089384400000000003</v>
+        <v>0.089353799999999997</v>
       </c>
       <c r="D57" s="467">
-        <v>-1.19</v>
+        <v>-1.2</v>
       </c>
       <c r="E57" s="468">
-        <v>0.23200000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F57" s="469">
-        <v>0.72759039999999997</v>
+        <v>0.72727149999999996</v>
       </c>
       <c r="G57" s="470">
-        <v>1.0802560000000001</v>
+        <v>1.0798160000000001</v>
       </c>
     </row>
     <row r="58">
@@ -11518,22 +11518,22 @@
         <v>53</v>
       </c>
       <c r="B58" s="473">
-        <v>0.69201299999999999</v>
+        <v>0.69304710000000003</v>
       </c>
       <c r="C58" s="474">
-        <v>0.061982000000000002</v>
+        <v>0.062080099999999999</v>
       </c>
       <c r="D58" s="475">
-        <v>-4.1100000000000003</v>
+        <v>-4.0899999999999999</v>
       </c>
       <c r="E58" s="476">
         <v>0</v>
       </c>
       <c r="F58" s="477">
-        <v>0.580596</v>
+        <v>0.58145480000000005</v>
       </c>
       <c r="G58" s="478">
-        <v>0.82481090000000001</v>
+        <v>0.82605620000000002</v>
       </c>
     </row>
     <row r="59">
@@ -11541,22 +11541,22 @@
         <v>54</v>
       </c>
       <c r="B59" s="481">
-        <v>1.2476400000000001</v>
+        <v>1.2488999999999999</v>
       </c>
       <c r="C59" s="482">
-        <v>0.1095322</v>
+        <v>0.1096491</v>
       </c>
       <c r="D59" s="483">
-        <v>2.52</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="E59" s="484">
-        <v>0.012</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="F59" s="485">
-        <v>1.0504150000000001</v>
+        <v>1.051466</v>
       </c>
       <c r="G59" s="486">
-        <v>1.481895</v>
+        <v>1.4834069999999999</v>
       </c>
     </row>
     <row r="60">
@@ -11564,22 +11564,22 @@
         <v>55</v>
       </c>
       <c r="B60" s="489">
-        <v>0.4519531</v>
+        <v>0.45302170000000003</v>
       </c>
       <c r="C60" s="490">
-        <v>0.4559897</v>
+        <v>0.4570883</v>
       </c>
       <c r="D60" s="491">
-        <v>-0.79000000000000004</v>
+        <v>-0.78000000000000003</v>
       </c>
       <c r="E60" s="492">
-        <v>0.431</v>
+        <v>0.433</v>
       </c>
       <c r="F60" s="493">
-        <v>0.062558900000000001</v>
+        <v>0.062701300000000001</v>
       </c>
       <c r="G60" s="494">
-        <v>3.2651059999999999</v>
+        <v>3.2731159999999999</v>
       </c>
     </row>
     <row r="61">
@@ -11587,22 +11587,22 @@
         <v>56</v>
       </c>
       <c r="B61" s="497">
-        <v>0.86644790000000005</v>
+        <v>0.86564149999999995</v>
       </c>
       <c r="C61" s="498">
-        <v>0.0336032</v>
+        <v>0.033577099999999999</v>
       </c>
       <c r="D61" s="499">
-        <v>-3.7000000000000002</v>
+        <v>-3.7200000000000002</v>
       </c>
       <c r="E61" s="500">
         <v>0</v>
       </c>
       <c r="F61" s="501">
-        <v>0.80302770000000001</v>
+        <v>0.80227090000000001</v>
       </c>
       <c r="G61" s="502">
-        <v>0.9348767</v>
+        <v>0.93401769999999995</v>
       </c>
     </row>
     <row r="62">
@@ -11610,22 +11610,22 @@
         <v>57</v>
       </c>
       <c r="B62" s="505">
-        <v>1.128463</v>
+        <v>1.129859</v>
       </c>
       <c r="C62" s="506">
-        <v>0.051392500000000001</v>
+        <v>0.051470200000000001</v>
       </c>
       <c r="D62" s="507">
-        <v>2.6499999999999999</v>
+        <v>2.6800000000000002</v>
       </c>
       <c r="E62" s="508">
-        <v>0.0080000000000000002</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="F62" s="509">
-        <v>1.0321</v>
+        <v>1.033352</v>
       </c>
       <c r="G62" s="510">
-        <v>1.2338229999999999</v>
+        <v>1.2353799999999999</v>
       </c>
     </row>
     <row r="63">
@@ -11633,22 +11633,22 @@
         <v>58</v>
       </c>
       <c r="B63" s="513">
-        <v>0.93404089999999995</v>
+        <v>0.93315870000000001</v>
       </c>
       <c r="C63" s="514">
-        <v>0.033977</v>
+        <v>0.033945299999999998</v>
       </c>
       <c r="D63" s="515">
-        <v>-1.8799999999999999</v>
+        <v>-1.8999999999999999</v>
       </c>
       <c r="E63" s="516">
-        <v>0.060999999999999999</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="F63" s="517">
-        <v>0.86976569999999998</v>
+        <v>0.86894349999999998</v>
       </c>
       <c r="G63" s="518">
-        <v>1.003066</v>
+        <v>1.0021199999999999</v>
       </c>
     </row>
     <row r="64">
@@ -11656,22 +11656,22 @@
         <v>59</v>
       </c>
       <c r="B64" s="521">
-        <v>1.2885549999999999</v>
+        <v>1.2892509999999999</v>
       </c>
       <c r="C64" s="522">
-        <v>0.11709700000000001</v>
+        <v>0.117183</v>
       </c>
       <c r="D64" s="523">
-        <v>2.79</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="E64" s="524">
         <v>0.0050000000000000001</v>
       </c>
       <c r="F64" s="525">
-        <v>1.0783259999999999</v>
+        <v>1.0788720000000001</v>
       </c>
       <c r="G64" s="526">
-        <v>1.539769</v>
+        <v>1.540654</v>
       </c>
     </row>
     <row r="65">
@@ -11679,22 +11679,22 @@
         <v>60</v>
       </c>
       <c r="B65" s="529">
-        <v>1.5311650000000001</v>
+        <v>1.5350360000000001</v>
       </c>
       <c r="C65" s="530">
-        <v>0.219363</v>
+        <v>0.2199845</v>
       </c>
       <c r="D65" s="531">
-        <v>2.9700000000000002</v>
+        <v>2.9900000000000002</v>
       </c>
       <c r="E65" s="532">
         <v>0.0030000000000000001</v>
       </c>
       <c r="F65" s="533">
-        <v>1.15631</v>
+        <v>1.1591340000000001</v>
       </c>
       <c r="G65" s="534">
-        <v>2.0275409999999998</v>
+        <v>2.0328409999999999</v>
       </c>
     </row>
     <row r="66">
@@ -11702,10 +11702,10 @@
         <v>61</v>
       </c>
       <c r="B66" s="537">
-        <v>0.24709629999999999</v>
+        <v>0.24660550000000001</v>
       </c>
       <c r="C66" s="538">
-        <v>0.33007350000000002</v>
+        <v>0.32937070000000002</v>
       </c>
       <c r="D66" s="539">
         <v>-1.05</v>
@@ -11714,10 +11714,10 @@
         <v>0.29499999999999999</v>
       </c>
       <c r="F66" s="541">
-        <v>0.018022799999999999</v>
+        <v>0.017993800000000001</v>
       </c>
       <c r="G66" s="542">
-        <v>3.3877329999999999</v>
+        <v>3.379737</v>
       </c>
     </row>
     <row r="67">
@@ -11725,22 +11725,22 @@
         <v>62</v>
       </c>
       <c r="B67" s="545">
-        <v>0.99148409999999998</v>
+        <v>0.99161860000000002</v>
       </c>
       <c r="C67" s="546">
-        <v>0.058413</v>
+        <v>0.058427199999999999</v>
       </c>
       <c r="D67" s="547">
-        <v>-0.15</v>
+        <v>-0.14000000000000001</v>
       </c>
       <c r="E67" s="548">
-        <v>0.88500000000000001</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="F67" s="549">
-        <v>0.88335940000000002</v>
+        <v>0.88346829999999999</v>
       </c>
       <c r="G67" s="550">
-        <v>1.112843</v>
+        <v>1.113008</v>
       </c>
     </row>
     <row r="68">
@@ -11748,22 +11748,22 @@
         <v>63</v>
       </c>
       <c r="B68" s="553">
-        <v>1.2773650000000001</v>
+        <v>1.2761499999999999</v>
       </c>
       <c r="C68" s="554">
-        <v>0.085905999999999996</v>
+        <v>0.085813799999999996</v>
       </c>
       <c r="D68" s="555">
-        <v>3.6400000000000001</v>
+        <v>3.6299999999999999</v>
       </c>
       <c r="E68" s="556">
         <v>0</v>
       </c>
       <c r="F68" s="557">
-        <v>1.119618</v>
+        <v>1.1185700000000001</v>
       </c>
       <c r="G68" s="558">
-        <v>1.457339</v>
+        <v>1.455929</v>
       </c>
     </row>
     <row r="69">
@@ -11771,22 +11771,22 @@
         <v>64</v>
       </c>
       <c r="B69" s="561">
-        <v>1.229684</v>
+        <v>1.2272650000000001</v>
       </c>
       <c r="C69" s="562">
-        <v>0.10766149999999999</v>
+        <v>0.1074454</v>
       </c>
       <c r="D69" s="563">
-        <v>2.3599999999999999</v>
+        <v>2.3399999999999999</v>
       </c>
       <c r="E69" s="564">
-        <v>0.017999999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="F69" s="565">
-        <v>1.035784</v>
+        <v>1.0337529999999999</v>
       </c>
       <c r="G69" s="566">
-        <v>1.459884</v>
+        <v>1.457001</v>
       </c>
     </row>
     <row r="70">
@@ -11794,22 +11794,22 @@
         <v>65</v>
       </c>
       <c r="B70" s="569">
-        <v>0.62965070000000001</v>
+        <v>0.63270329999999997</v>
       </c>
       <c r="C70" s="570">
-        <v>0.27697549999999999</v>
+        <v>0.27850580000000003</v>
       </c>
       <c r="D70" s="571">
-        <v>-1.05</v>
+        <v>-1.04</v>
       </c>
       <c r="E70" s="572">
-        <v>0.29299999999999998</v>
+        <v>0.29799999999999999</v>
       </c>
       <c r="F70" s="573">
-        <v>0.2658684</v>
+        <v>0.26700220000000002</v>
       </c>
       <c r="G70" s="574">
-        <v>1.4911890000000001</v>
+        <v>1.4992890000000001</v>
       </c>
     </row>
     <row r="71">
@@ -11817,22 +11817,22 @@
         <v>66</v>
       </c>
       <c r="B71" s="577">
-        <v>1.94034</v>
+        <v>1.9363870000000001</v>
       </c>
       <c r="C71" s="578">
-        <v>0.30414930000000001</v>
+        <v>0.3035931</v>
       </c>
       <c r="D71" s="579">
-        <v>4.2300000000000004</v>
+        <v>4.21</v>
       </c>
       <c r="E71" s="580">
         <v>0</v>
       </c>
       <c r="F71" s="581">
-        <v>1.42709</v>
+        <v>1.424091</v>
       </c>
       <c r="G71" s="582">
-        <v>2.6381779999999999</v>
+        <v>2.6329720000000001</v>
       </c>
     </row>
     <row r="72">
@@ -11840,22 +11840,22 @@
         <v>67</v>
       </c>
       <c r="B72" s="585">
-        <v>1.001576</v>
+        <v>1.0026330000000001</v>
       </c>
       <c r="C72" s="586">
-        <v>0.17293890000000001</v>
+        <v>0.17313439999999999</v>
       </c>
       <c r="D72" s="587">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E72" s="588">
-        <v>0.99299999999999999</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="F72" s="589">
-        <v>0.71401879999999995</v>
+        <v>0.71475420000000001</v>
       </c>
       <c r="G72" s="590">
-        <v>1.404941</v>
+        <v>1.40646</v>
       </c>
     </row>
     <row r="73">
@@ -11863,22 +11863,22 @@
         <v>68</v>
       </c>
       <c r="B73" s="593">
-        <v>0.95334750000000001</v>
+        <v>0.95309200000000005</v>
       </c>
       <c r="C73" s="594">
-        <v>0.0764156</v>
+        <v>0.076392500000000002</v>
       </c>
       <c r="D73" s="595">
         <v>-0.59999999999999998</v>
       </c>
       <c r="E73" s="596">
-        <v>0.55100000000000005</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="F73" s="597">
-        <v>0.81474780000000002</v>
+        <v>0.81453379999999998</v>
       </c>
       <c r="G73" s="598">
-        <v>1.1155250000000001</v>
+        <v>1.1152200000000001</v>
       </c>
     </row>
     <row r="74">
@@ -11886,22 +11886,22 @@
         <v>69</v>
       </c>
       <c r="B74" s="601">
-        <v>1.1366540000000001</v>
+        <v>1.136344</v>
       </c>
       <c r="C74" s="602">
-        <v>0.1266128</v>
+        <v>0.12661159999999999</v>
       </c>
       <c r="D74" s="603">
         <v>1.1499999999999999</v>
       </c>
       <c r="E74" s="604">
-        <v>0.25</v>
+        <v>0.251</v>
       </c>
       <c r="F74" s="605">
-        <v>0.91371860000000005</v>
+        <v>0.91341649999999997</v>
       </c>
       <c r="G74" s="606">
-        <v>1.4139839999999999</v>
+        <v>1.4136789999999999</v>
       </c>
     </row>
     <row r="75">
@@ -11909,22 +11909,22 @@
         <v>70</v>
       </c>
       <c r="B75" s="609">
-        <v>1.0105789999999999</v>
+        <v>1.017245</v>
       </c>
       <c r="C75" s="610">
-        <v>0.035886599999999998</v>
+        <v>0.036282300000000004</v>
       </c>
       <c r="D75" s="611">
-        <v>0.29999999999999999</v>
+        <v>0.47999999999999998</v>
       </c>
       <c r="E75" s="612">
-        <v>0.76700000000000002</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="F75" s="613">
-        <v>0.94263450000000004</v>
+        <v>0.94856189999999996</v>
       </c>
       <c r="G75" s="614">
-        <v>1.083421</v>
+        <v>1.090902</v>
       </c>
     </row>
     <row r="76">
@@ -11932,22 +11932,22 @@
         <v>71</v>
       </c>
       <c r="B76" s="617">
-        <v>1.341038</v>
+        <v>1.3648549999999999</v>
       </c>
       <c r="C76" s="618">
-        <v>0.1168526</v>
+        <v>0.11955250000000001</v>
       </c>
       <c r="D76" s="619">
-        <v>3.3700000000000001</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="E76" s="620">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F76" s="621">
-        <v>1.1305000000000001</v>
+        <v>1.1495470000000001</v>
       </c>
       <c r="G76" s="622">
-        <v>1.590784</v>
+        <v>1.62049</v>
       </c>
     </row>
     <row r="77">
@@ -11955,22 +11955,22 @@
         <v>72</v>
       </c>
       <c r="B77" s="625">
-        <v>1.0341370000000001</v>
+        <v>1.0294509999999999</v>
       </c>
       <c r="C77" s="626">
-        <v>0.043159500000000004</v>
+        <v>0.043019700000000001</v>
       </c>
       <c r="D77" s="627">
-        <v>0.80000000000000004</v>
+        <v>0.68999999999999995</v>
       </c>
       <c r="E77" s="628">
-        <v>0.42099999999999999</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="F77" s="629">
-        <v>0.95291269999999995</v>
+        <v>0.94849459999999997</v>
       </c>
       <c r="G77" s="630">
-        <v>1.1222840000000001</v>
+        <v>1.1173169999999999</v>
       </c>
     </row>
     <row r="78">
@@ -11978,22 +11978,22 @@
         <v>73</v>
       </c>
       <c r="B78" s="633">
-        <v>1.1118440000000001</v>
+        <v>1.114568</v>
       </c>
       <c r="C78" s="634">
-        <v>0.1663501</v>
+        <v>0.1667701</v>
       </c>
       <c r="D78" s="635">
-        <v>0.70999999999999997</v>
+        <v>0.71999999999999997</v>
       </c>
       <c r="E78" s="636">
-        <v>0.47899999999999998</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="F78" s="637">
-        <v>0.82925939999999998</v>
+        <v>0.83127189999999995</v>
       </c>
       <c r="G78" s="638">
-        <v>1.490726</v>
+        <v>1.49441</v>
       </c>
     </row>
     <row r="79">
@@ -12001,22 +12001,22 @@
         <v>74</v>
       </c>
       <c r="B79" s="641">
-        <v>1.1200490000000001</v>
+        <v>1.120684</v>
       </c>
       <c r="C79" s="642">
-        <v>0.038449400000000002</v>
+        <v>0.038473800000000002</v>
       </c>
       <c r="D79" s="643">
-        <v>3.2999999999999998</v>
+        <v>3.3199999999999999</v>
       </c>
       <c r="E79" s="644">
         <v>0.001</v>
       </c>
       <c r="F79" s="645">
-        <v>1.0471680000000001</v>
+        <v>1.047758</v>
       </c>
       <c r="G79" s="646">
-        <v>1.1980010000000001</v>
+        <v>1.1986859999999999</v>
       </c>
     </row>
     <row r="80">
@@ -12024,22 +12024,22 @@
         <v>75</v>
       </c>
       <c r="B80" s="656">
-        <v>105.6007</v>
+        <v>79.053520000000006</v>
       </c>
       <c r="C80" s="657">
-        <v>44.021410000000003</v>
+        <v>35.161259999999999</v>
       </c>
       <c r="D80" s="658">
-        <v>11.18</v>
+        <v>9.8300000000000001</v>
       </c>
       <c r="E80" s="659">
         <v>0</v>
       </c>
       <c r="F80" s="660">
-        <v>46.647559999999999</v>
+        <v>33.061729999999997</v>
       </c>
       <c r="G80" s="661">
-        <v>239.05860000000001</v>
+        <v>189.024</v>
       </c>
     </row>
   </sheetData>
